--- a/output/Bracket_2921951930876837779.xlsx
+++ b/output/Bracket_2921951930876837779.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amgal\Documents\Data Science\KingfisherCourt\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ED0973D-0B0D-4055-8456-CD1FCC7C808F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5D029D-0010-46DC-BC58-33F66B5DC0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7115,17 +7115,110 @@
     <xf numFmtId="0" fontId="46" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7160,33 +7253,6 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7204,72 +7270,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -21744,47 +21744,47 @@
   <sheetData>
     <row r="1" spans="1:47" s="6" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="281" t="s">
+      <c r="B1" s="279" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="281"/>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
-      <c r="F1" s="281"/>
-      <c r="G1" s="281"/>
-      <c r="H1" s="281"/>
-      <c r="I1" s="281"/>
-      <c r="J1" s="281"/>
-      <c r="K1" s="281"/>
-      <c r="L1" s="281"/>
-      <c r="M1" s="281"/>
-      <c r="N1" s="281"/>
-      <c r="O1" s="281"/>
-      <c r="P1" s="281"/>
-      <c r="Q1" s="281"/>
-      <c r="R1" s="281"/>
-      <c r="S1" s="281"/>
-      <c r="T1" s="281"/>
-      <c r="U1" s="281"/>
-      <c r="V1" s="281"/>
-      <c r="W1" s="281"/>
-      <c r="X1" s="281"/>
-      <c r="Y1" s="281"/>
-      <c r="Z1" s="281"/>
-      <c r="AA1" s="281"/>
-      <c r="AB1" s="281"/>
-      <c r="AC1" s="281"/>
-      <c r="AD1" s="281"/>
-      <c r="AE1" s="281"/>
-      <c r="AF1" s="281"/>
-      <c r="AG1" s="281"/>
-      <c r="AH1" s="281"/>
-      <c r="AI1" s="281"/>
-      <c r="AJ1" s="281"/>
-      <c r="AK1" s="281"/>
-      <c r="AL1" s="281"/>
-      <c r="AM1" s="281"/>
-      <c r="AN1" s="281"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="279"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="279"/>
+      <c r="O1" s="279"/>
+      <c r="P1" s="279"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="279"/>
+      <c r="S1" s="279"/>
+      <c r="T1" s="279"/>
+      <c r="U1" s="279"/>
+      <c r="V1" s="279"/>
+      <c r="W1" s="279"/>
+      <c r="X1" s="279"/>
+      <c r="Y1" s="279"/>
+      <c r="Z1" s="279"/>
+      <c r="AA1" s="279"/>
+      <c r="AB1" s="279"/>
+      <c r="AC1" s="279"/>
+      <c r="AD1" s="279"/>
+      <c r="AE1" s="279"/>
+      <c r="AF1" s="279"/>
+      <c r="AG1" s="279"/>
+      <c r="AH1" s="279"/>
+      <c r="AI1" s="279"/>
+      <c r="AJ1" s="279"/>
+      <c r="AK1" s="279"/>
+      <c r="AL1" s="279"/>
+      <c r="AM1" s="279"/>
+      <c r="AN1" s="279"/>
       <c r="AO1" s="17"/>
     </row>
     <row r="2" spans="1:47" s="63" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -21816,13 +21816,13 @@
       <c r="P2" s="61"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
-      <c r="S2" s="285" t="s">
+      <c r="S2" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="285"/>
-      <c r="U2" s="285"/>
-      <c r="V2" s="285"/>
-      <c r="W2" s="285"/>
+      <c r="T2" s="281"/>
+      <c r="U2" s="281"/>
+      <c r="V2" s="281"/>
+      <c r="W2" s="281"/>
       <c r="X2" s="62"/>
       <c r="Y2" s="62"/>
       <c r="Z2" s="62"/>
@@ -21900,7 +21900,7 @@
       <c r="AM3" s="22"/>
       <c r="AN3" s="22"/>
       <c r="AO3" s="17"/>
-      <c r="AQ3" s="288"/>
+      <c r="AQ3" s="275"/>
       <c r="AU3" s="7" t="s">
         <v>17</v>
       </c>
@@ -21932,7 +21932,7 @@
       <c r="AM4" s="26"/>
       <c r="AN4" s="24"/>
       <c r="AO4" s="17"/>
-      <c r="AQ4" s="288"/>
+      <c r="AQ4" s="275"/>
     </row>
     <row r="5" spans="1:47" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16"/>
@@ -21951,15 +21951,15 @@
         <f>Games!L5</f>
         <v>0.19</v>
       </c>
-      <c r="F5" s="262" t="str">
+      <c r="F5" s="256" t="str">
         <f>Games!O5</f>
         <v>Buffalo</v>
       </c>
-      <c r="G5" s="247" t="e" vm="66">
+      <c r="G5" s="259" t="e" vm="66">
         <f>_xlfn.XLOOKUP(F5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H5" s="284">
+      <c r="H5" s="280">
         <f>Games!L38</f>
         <v>0.51</v>
       </c>
@@ -21979,15 +21979,15 @@
       <c r="AA5" s="25"/>
       <c r="AD5" s="25"/>
       <c r="AG5" s="25"/>
-      <c r="AH5" s="264">
+      <c r="AH5" s="251">
         <f>Games!L46</f>
         <v>0</v>
       </c>
-      <c r="AI5" s="297" t="e" vm="97">
+      <c r="AI5" s="247" t="e" vm="97">
         <f>_xlfn.XLOOKUP(AJ5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ5" s="262" t="str">
+      <c r="AJ5" s="256" t="str">
         <f>Games!O21</f>
         <v>Abilene Christian</v>
       </c>
@@ -22007,14 +22007,14 @@
         <v>1</v>
       </c>
       <c r="AO5" s="17"/>
-      <c r="AQ5" s="288"/>
+      <c r="AQ5" s="275"/>
       <c r="AU5" s="2" t="b">
         <f>IF(AP29="x",TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="283">
+      <c r="A6" s="255">
         <f>IF($AU$5=TRUE,1,"")</f>
         <v>1</v>
       </c>
@@ -22022,9 +22022,9 @@
       <c r="C6" s="38"/>
       <c r="D6" s="71"/>
       <c r="E6" s="47"/>
-      <c r="F6" s="263"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="265"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="260"/>
+      <c r="H6" s="252"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="L6" s="25"/>
@@ -22041,20 +22041,20 @@
       <c r="AA6" s="25"/>
       <c r="AD6" s="25"/>
       <c r="AG6" s="25"/>
-      <c r="AH6" s="265"/>
-      <c r="AI6" s="298"/>
-      <c r="AJ6" s="263"/>
+      <c r="AH6" s="252"/>
+      <c r="AI6" s="248"/>
+      <c r="AJ6" s="257"/>
       <c r="AK6" s="55"/>
       <c r="AM6" s="39"/>
       <c r="AN6" s="28"/>
-      <c r="AO6" s="287">
+      <c r="AO6" s="277">
         <f>IF($AU$5=TRUE,A66+1,"")</f>
         <v>17</v>
       </c>
-      <c r="AQ6" s="288"/>
+      <c r="AQ6" s="275"/>
     </row>
     <row r="7" spans="1:47" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="283"/>
+      <c r="A7" s="255"/>
       <c r="B7" s="27">
         <v>16</v>
       </c>
@@ -22070,21 +22070,21 @@
         <f>Games!N5</f>
         <v>0.81</v>
       </c>
-      <c r="F7" s="282">
+      <c r="F7" s="276">
         <f>IF($AU$5=TRUE,AO66+1,"")</f>
         <v>33</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="49"/>
-      <c r="I7" s="279" t="str">
+      <c r="I7" s="265" t="str">
         <f>Games!O38</f>
         <v>Buffalo</v>
       </c>
-      <c r="J7" s="247" t="e" vm="66">
+      <c r="J7" s="259" t="e" vm="66">
         <f>_xlfn.XLOOKUP(I7,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="264">
+      <c r="K7" s="251">
         <f>Games!L55</f>
         <v>0.41</v>
       </c>
@@ -22101,21 +22101,21 @@
       <c r="X7" s="25"/>
       <c r="AA7" s="25"/>
       <c r="AD7" s="25"/>
-      <c r="AE7" s="264">
+      <c r="AE7" s="251">
         <f>Games!L59</f>
         <v>0.99</v>
       </c>
-      <c r="AF7" s="297" t="e" vm="100">
+      <c r="AF7" s="247" t="e" vm="100">
         <f>_xlfn.XLOOKUP(AG7,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG7" s="262" t="str">
+      <c r="AG7" s="256" t="str">
         <f>Games!O46</f>
         <v>Alabama</v>
       </c>
       <c r="AH7" s="55"/>
       <c r="AI7" s="51"/>
-      <c r="AJ7" s="282">
+      <c r="AJ7" s="276">
         <f>IF($AU$5=TRUE,F63+1,"")</f>
         <v>41</v>
       </c>
@@ -22134,20 +22134,20 @@
       <c r="AN7" s="27">
         <v>16</v>
       </c>
-      <c r="AO7" s="287"/>
-      <c r="AQ7" s="288"/>
+      <c r="AO7" s="277"/>
+      <c r="AQ7" s="275"/>
     </row>
     <row r="8" spans="1:47" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16"/>
       <c r="B8" s="28"/>
       <c r="C8" s="38"/>
       <c r="D8" s="71"/>
-      <c r="F8" s="283"/>
+      <c r="F8" s="255"/>
       <c r="G8" s="15"/>
       <c r="H8" s="50"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="248"/>
-      <c r="K8" s="265"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="260"/>
+      <c r="K8" s="252"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="O8" s="25"/>
@@ -22161,15 +22161,15 @@
       <c r="X8" s="25"/>
       <c r="AA8" s="25"/>
       <c r="AD8" s="25"/>
-      <c r="AE8" s="265"/>
-      <c r="AF8" s="298"/>
-      <c r="AG8" s="263"/>
+      <c r="AE8" s="252"/>
+      <c r="AF8" s="248"/>
+      <c r="AG8" s="257"/>
       <c r="AH8" s="56"/>
-      <c r="AJ8" s="283"/>
+      <c r="AJ8" s="255"/>
       <c r="AM8" s="39"/>
       <c r="AN8" s="28"/>
       <c r="AO8" s="17"/>
-      <c r="AQ8" s="288"/>
+      <c r="AQ8" s="275"/>
     </row>
     <row r="9" spans="1:47" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16"/>
@@ -22188,15 +22188,15 @@
         <f>Games!L6</f>
         <v>0.7</v>
       </c>
-      <c r="F9" s="262" t="str">
+      <c r="F9" s="256" t="str">
         <f>Games!O6</f>
         <v>Butler</v>
       </c>
-      <c r="G9" s="247" t="e" vm="67">
+      <c r="G9" s="259" t="e" vm="67">
         <f>_xlfn.XLOOKUP(F9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H9" s="277">
+      <c r="H9" s="261">
         <f>Games!N38</f>
         <v>0.49</v>
       </c>
@@ -22218,15 +22218,15 @@
       <c r="AD9" s="25"/>
       <c r="AE9" s="55"/>
       <c r="AG9" s="24"/>
-      <c r="AH9" s="269">
+      <c r="AH9" s="253">
         <f>Games!N46</f>
         <v>1</v>
       </c>
-      <c r="AI9" s="297" t="e" vm="100">
+      <c r="AI9" s="247" t="e" vm="100">
         <f>_xlfn.XLOOKUP(AJ9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ9" s="262" t="str">
+      <c r="AJ9" s="256" t="str">
         <f>Games!O22</f>
         <v>Alabama</v>
       </c>
@@ -22246,10 +22246,10 @@
         <v>8</v>
       </c>
       <c r="AO9" s="17"/>
-      <c r="AQ9" s="288"/>
+      <c r="AQ9" s="275"/>
     </row>
     <row r="10" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="286">
+      <c r="A10" s="278">
         <f>IF($AU$5=TRUE,A6+1,"")</f>
         <v>2</v>
       </c>
@@ -22257,9 +22257,9 @@
       <c r="C10" s="38"/>
       <c r="D10" s="71"/>
       <c r="E10" s="47"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="278"/>
+      <c r="F10" s="257"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="262"/>
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="50"/>
@@ -22278,20 +22278,20 @@
       <c r="AD10" s="25"/>
       <c r="AE10" s="56"/>
       <c r="AG10" s="24"/>
-      <c r="AH10" s="270"/>
-      <c r="AI10" s="298"/>
-      <c r="AJ10" s="263"/>
+      <c r="AH10" s="254"/>
+      <c r="AI10" s="248"/>
+      <c r="AJ10" s="257"/>
       <c r="AK10" s="55"/>
       <c r="AM10" s="39"/>
       <c r="AN10" s="28"/>
-      <c r="AO10" s="287">
+      <c r="AO10" s="277">
         <f>IF($AU$5=TRUE,AO6+1,"")</f>
         <v>18</v>
       </c>
-      <c r="AQ10" s="288"/>
+      <c r="AQ10" s="275"/>
     </row>
     <row r="11" spans="1:47" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="286"/>
+      <c r="A11" s="278"/>
       <c r="B11" s="27">
         <v>9</v>
       </c>
@@ -22309,21 +22309,21 @@
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
-      <c r="I11" s="283">
+      <c r="I11" s="255">
         <f>IF($AU$5=TRUE,AJ63+1,"")</f>
         <v>49</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="50"/>
-      <c r="L11" s="279" t="str">
+      <c r="L11" s="265" t="str">
         <f>Games!O55</f>
         <v>Cal State Northridge</v>
       </c>
-      <c r="M11" s="247" t="e" vm="71">
+      <c r="M11" s="259" t="e" vm="71">
         <f>_xlfn.XLOOKUP(L11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N11" s="264">
+      <c r="N11" s="251">
         <f>Games!L64</f>
         <v>0.36</v>
       </c>
@@ -22331,16 +22331,16 @@
       <c r="P11" s="25"/>
       <c r="R11" s="25"/>
       <c r="S11" s="25"/>
-      <c r="T11" s="251" t="e" vm="92">
+      <c r="T11" s="282" t="e" vm="92">
         <f>_xlfn.XLOOKUP(S32,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U11" s="252"/>
-      <c r="V11" s="253"/>
+      <c r="U11" s="283"/>
+      <c r="V11" s="284"/>
       <c r="W11" s="25"/>
       <c r="X11" s="25"/>
       <c r="AA11" s="25"/>
-      <c r="AB11" s="264">
+      <c r="AB11" s="251">
         <f>Games!L66</f>
         <v>0.77</v>
       </c>
@@ -22348,12 +22348,12 @@
         <f>_xlfn.XLOOKUP(AD11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD11" s="262" t="str">
+      <c r="AD11" s="256" t="str">
         <f>Games!O59</f>
         <v>Alabama</v>
       </c>
       <c r="AE11" s="56"/>
-      <c r="AG11" s="283">
+      <c r="AG11" s="255">
         <f>IF($AU$5=TRUE,I59+1,"")</f>
         <v>53</v>
       </c>
@@ -22373,8 +22373,8 @@
       <c r="AN11" s="27">
         <v>9</v>
       </c>
-      <c r="AO11" s="287"/>
-      <c r="AQ11" s="288"/>
+      <c r="AO11" s="277"/>
+      <c r="AQ11" s="275"/>
     </row>
     <row r="12" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
@@ -22383,27 +22383,27 @@
       <c r="D12" s="71"/>
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
-      <c r="I12" s="283"/>
+      <c r="I12" s="255"/>
       <c r="J12" s="15"/>
       <c r="K12" s="50"/>
-      <c r="L12" s="280"/>
-      <c r="M12" s="248"/>
-      <c r="N12" s="265"/>
+      <c r="L12" s="266"/>
+      <c r="M12" s="260"/>
+      <c r="N12" s="252"/>
       <c r="O12" s="25"/>
       <c r="P12" s="25"/>
       <c r="R12" s="25"/>
       <c r="S12" s="25"/>
-      <c r="T12" s="254"/>
-      <c r="U12" s="255"/>
-      <c r="V12" s="256"/>
+      <c r="T12" s="285"/>
+      <c r="U12" s="286"/>
+      <c r="V12" s="287"/>
       <c r="W12" s="25"/>
       <c r="X12" s="25"/>
       <c r="AA12" s="25"/>
-      <c r="AB12" s="265"/>
+      <c r="AB12" s="252"/>
       <c r="AC12" s="250"/>
-      <c r="AD12" s="263"/>
+      <c r="AD12" s="257"/>
       <c r="AE12" s="56"/>
-      <c r="AG12" s="283"/>
+      <c r="AG12" s="255"/>
       <c r="AJ12" s="24"/>
       <c r="AM12" s="39"/>
       <c r="AN12" s="28"/>
@@ -22426,15 +22426,15 @@
         <f>Games!L7</f>
         <v>0.2</v>
       </c>
-      <c r="F13" s="262" t="str">
+      <c r="F13" s="256" t="str">
         <f>Games!O7</f>
         <v>Cal State Fullerton</v>
       </c>
-      <c r="G13" s="247" t="e" vm="70">
+      <c r="G13" s="259" t="e" vm="70">
         <f>_xlfn.XLOOKUP(F13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H13" s="264">
+      <c r="H13" s="251">
         <f>Games!L39</f>
         <v>0.25</v>
       </c>
@@ -22448,9 +22448,9 @@
       <c r="P13" s="25"/>
       <c r="R13" s="25"/>
       <c r="S13" s="25"/>
-      <c r="T13" s="254"/>
-      <c r="U13" s="255"/>
-      <c r="V13" s="256"/>
+      <c r="T13" s="285"/>
+      <c r="U13" s="286"/>
+      <c r="V13" s="287"/>
       <c r="W13" s="25"/>
       <c r="X13" s="25"/>
       <c r="AA13" s="25"/>
@@ -22458,7 +22458,7 @@
       <c r="AD13" s="25"/>
       <c r="AE13" s="56"/>
       <c r="AG13" s="24"/>
-      <c r="AH13" s="264">
+      <c r="AH13" s="251">
         <f>Games!L47</f>
         <v>0.59</v>
       </c>
@@ -22466,7 +22466,7 @@
         <f>_xlfn.XLOOKUP(AJ13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ13" s="262" t="str">
+      <c r="AJ13" s="256" t="str">
         <f>Games!O23</f>
         <v>Alabama A&amp;M</v>
       </c>
@@ -22489,7 +22489,7 @@
       <c r="AQ13" s="9"/>
     </row>
     <row r="14" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="283">
+      <c r="A14" s="255">
         <f>IF($AU$5=TRUE,A10+1,"")</f>
         <v>3</v>
       </c>
@@ -22497,9 +22497,9 @@
       <c r="C14" s="38"/>
       <c r="D14" s="71"/>
       <c r="E14" s="49"/>
-      <c r="F14" s="263"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="265"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="260"/>
+      <c r="H14" s="252"/>
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="50"/>
@@ -22510,9 +22510,9 @@
       <c r="P14" s="25"/>
       <c r="R14" s="25"/>
       <c r="S14" s="25"/>
-      <c r="T14" s="254"/>
-      <c r="U14" s="255"/>
-      <c r="V14" s="256"/>
+      <c r="T14" s="285"/>
+      <c r="U14" s="286"/>
+      <c r="V14" s="287"/>
       <c r="W14" s="25"/>
       <c r="X14" s="25"/>
       <c r="AA14" s="25"/>
@@ -22520,20 +22520,20 @@
       <c r="AD14" s="25"/>
       <c r="AE14" s="56"/>
       <c r="AG14" s="24"/>
-      <c r="AH14" s="265"/>
+      <c r="AH14" s="252"/>
       <c r="AI14" s="250"/>
-      <c r="AJ14" s="263"/>
+      <c r="AJ14" s="257"/>
       <c r="AK14" s="55"/>
       <c r="AM14" s="39"/>
       <c r="AN14" s="28"/>
-      <c r="AO14" s="287">
+      <c r="AO14" s="277">
         <f>IF($AU$5=TRUE,AO10+1,"")</f>
         <v>19</v>
       </c>
-      <c r="AQ14" s="288"/>
+      <c r="AQ14" s="275"/>
     </row>
     <row r="15" spans="1:47" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="283"/>
+      <c r="A15" s="255"/>
       <c r="B15" s="27">
         <v>12</v>
       </c>
@@ -22549,21 +22549,21 @@
         <f>Games!N7</f>
         <v>0.8</v>
       </c>
-      <c r="F15" s="282">
+      <c r="F15" s="276">
         <f>IF($AU$5=TRUE,F7+1,"")</f>
         <v>34</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="49"/>
-      <c r="I15" s="279" t="str">
+      <c r="I15" s="265" t="str">
         <f>Games!O39</f>
         <v>Cal State Northridge</v>
       </c>
-      <c r="J15" s="247" t="e" vm="71">
+      <c r="J15" s="259" t="e" vm="71">
         <f>_xlfn.XLOOKUP(I15,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="277">
+      <c r="K15" s="261">
         <f>Games!N55</f>
         <v>0.59</v>
       </c>
@@ -22574,15 +22574,15 @@
       <c r="P15" s="25"/>
       <c r="R15" s="25"/>
       <c r="S15" s="25"/>
-      <c r="T15" s="254"/>
-      <c r="U15" s="255"/>
-      <c r="V15" s="256"/>
+      <c r="T15" s="285"/>
+      <c r="U15" s="286"/>
+      <c r="V15" s="287"/>
       <c r="W15" s="25"/>
       <c r="X15" s="25"/>
       <c r="AA15" s="25"/>
       <c r="AB15" s="56"/>
       <c r="AD15" s="25"/>
-      <c r="AE15" s="269">
+      <c r="AE15" s="253">
         <f>Games!N59</f>
         <v>0.01</v>
       </c>
@@ -22590,13 +22590,13 @@
         <f>_xlfn.XLOOKUP(AG15,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG15" s="262" t="str">
+      <c r="AG15" s="256" t="str">
         <f>Games!O47</f>
         <v>Alabama A&amp;M</v>
       </c>
       <c r="AH15" s="55"/>
       <c r="AI15" s="51"/>
-      <c r="AJ15" s="282">
+      <c r="AJ15" s="276">
         <f>IF($AU$5=TRUE,AJ7+1,"")</f>
         <v>42</v>
       </c>
@@ -22615,20 +22615,20 @@
       <c r="AN15" s="27">
         <v>12</v>
       </c>
-      <c r="AO15" s="287"/>
-      <c r="AQ15" s="288"/>
+      <c r="AO15" s="277"/>
+      <c r="AQ15" s="275"/>
     </row>
     <row r="16" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="28"/>
       <c r="C16" s="38"/>
       <c r="D16" s="71"/>
-      <c r="F16" s="283"/>
+      <c r="F16" s="255"/>
       <c r="G16" s="15"/>
       <c r="H16" s="50"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="248"/>
-      <c r="K16" s="278"/>
+      <c r="I16" s="266"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="262"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="50"/>
@@ -22636,23 +22636,23 @@
       <c r="P16" s="25"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
-      <c r="T16" s="254"/>
-      <c r="U16" s="255"/>
-      <c r="V16" s="256"/>
+      <c r="T16" s="285"/>
+      <c r="U16" s="286"/>
+      <c r="V16" s="287"/>
       <c r="W16" s="25"/>
       <c r="X16" s="25"/>
       <c r="AA16" s="25"/>
       <c r="AB16" s="56"/>
       <c r="AD16" s="25"/>
-      <c r="AE16" s="270"/>
+      <c r="AE16" s="254"/>
       <c r="AF16" s="250"/>
-      <c r="AG16" s="263"/>
+      <c r="AG16" s="257"/>
       <c r="AH16" s="56"/>
-      <c r="AJ16" s="283"/>
+      <c r="AJ16" s="255"/>
       <c r="AM16" s="39"/>
       <c r="AN16" s="28"/>
       <c r="AO16" s="17"/>
-      <c r="AQ16" s="288"/>
+      <c r="AQ16" s="275"/>
     </row>
     <row r="17" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
@@ -22671,15 +22671,15 @@
         <f>Games!L8</f>
         <v>0.52</v>
       </c>
-      <c r="F17" s="262" t="str">
+      <c r="F17" s="256" t="str">
         <f>Games!O8</f>
         <v>Cal State Northridge</v>
       </c>
-      <c r="G17" s="247" t="e" vm="71">
+      <c r="G17" s="259" t="e" vm="71">
         <f>_xlfn.XLOOKUP(F17,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="277">
+      <c r="H17" s="261">
         <f>Games!N39</f>
         <v>0.75</v>
       </c>
@@ -22692,16 +22692,16 @@
       <c r="P17" s="25"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
-      <c r="T17" s="254"/>
-      <c r="U17" s="255"/>
-      <c r="V17" s="256"/>
+      <c r="T17" s="285"/>
+      <c r="U17" s="286"/>
+      <c r="V17" s="287"/>
       <c r="W17" s="25"/>
       <c r="X17" s="25"/>
       <c r="AA17" s="25"/>
       <c r="AB17" s="56"/>
       <c r="AD17" s="25"/>
       <c r="AG17" s="24"/>
-      <c r="AH17" s="269">
+      <c r="AH17" s="253">
         <f>Games!N47</f>
         <v>0.41</v>
       </c>
@@ -22709,7 +22709,7 @@
         <f>_xlfn.XLOOKUP(AJ17,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ17" s="262" t="str">
+      <c r="AJ17" s="256" t="str">
         <f>Games!O24</f>
         <v>Albany (NY)</v>
       </c>
@@ -22729,10 +22729,10 @@
         <v>4</v>
       </c>
       <c r="AO17" s="17"/>
-      <c r="AQ17" s="288"/>
+      <c r="AQ17" s="275"/>
     </row>
     <row r="18" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="283">
+      <c r="A18" s="255">
         <f>IF($AU$5=TRUE,A14+1,"")</f>
         <v>4</v>
       </c>
@@ -22740,9 +22740,9 @@
       <c r="C18" s="38"/>
       <c r="D18" s="71"/>
       <c r="E18" s="49"/>
-      <c r="F18" s="263"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="278"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="262"/>
       <c r="I18" s="24"/>
       <c r="J18" s="24"/>
       <c r="L18" s="25"/>
@@ -22752,29 +22752,29 @@
       <c r="P18" s="25"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
-      <c r="T18" s="254"/>
-      <c r="U18" s="255"/>
-      <c r="V18" s="256"/>
+      <c r="T18" s="285"/>
+      <c r="U18" s="286"/>
+      <c r="V18" s="287"/>
       <c r="W18" s="25"/>
       <c r="X18" s="25"/>
       <c r="AA18" s="25"/>
       <c r="AB18" s="56"/>
       <c r="AD18" s="25"/>
       <c r="AG18" s="24"/>
-      <c r="AH18" s="270"/>
+      <c r="AH18" s="254"/>
       <c r="AI18" s="250"/>
-      <c r="AJ18" s="263"/>
+      <c r="AJ18" s="257"/>
       <c r="AK18" s="55"/>
       <c r="AM18" s="39"/>
       <c r="AN18" s="28"/>
-      <c r="AO18" s="287">
+      <c r="AO18" s="277">
         <f>IF($AU$5=TRUE,AO14+1,"")</f>
         <v>20</v>
       </c>
-      <c r="AQ18" s="288"/>
+      <c r="AQ18" s="275"/>
     </row>
     <row r="19" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="283"/>
+      <c r="A19" s="255"/>
       <c r="B19" s="27">
         <v>13</v>
       </c>
@@ -22794,32 +22794,32 @@
       <c r="G19" s="24"/>
       <c r="I19" s="24"/>
       <c r="J19" s="24"/>
-      <c r="K19" s="266" t="s">
+      <c r="K19" s="258" t="s">
         <v>15</v>
       </c>
-      <c r="L19" s="266"/>
+      <c r="L19" s="258"/>
       <c r="M19" s="20"/>
       <c r="N19" s="50"/>
-      <c r="O19" s="279" t="str">
+      <c r="O19" s="265" t="str">
         <f>Games!O64</f>
         <v>Central Arkansas</v>
       </c>
-      <c r="P19" s="247" t="e" vm="76">
+      <c r="P19" s="259" t="e" vm="76">
         <f>_xlfn.XLOOKUP(O19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q19" s="264">
+      <c r="Q19" s="251">
         <f>Games!L69</f>
         <v>0.21</v>
       </c>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
-      <c r="T19" s="257"/>
-      <c r="U19" s="258"/>
-      <c r="V19" s="259"/>
+      <c r="T19" s="288"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="290"/>
       <c r="W19" s="25"/>
       <c r="X19" s="25"/>
-      <c r="Y19" s="264">
+      <c r="Y19" s="251">
         <f>Games!L70</f>
         <v>0.68</v>
       </c>
@@ -22827,15 +22827,15 @@
         <f>_xlfn.XLOOKUP(AA19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA19" s="262" t="str">
+      <c r="AA19" s="256" t="str">
         <f>Games!O66</f>
         <v>Alabama</v>
       </c>
       <c r="AB19" s="56"/>
-      <c r="AD19" s="266" t="s">
+      <c r="AD19" s="258" t="s">
         <v>3</v>
       </c>
-      <c r="AE19" s="266"/>
+      <c r="AE19" s="258"/>
       <c r="AF19" s="20"/>
       <c r="AG19" s="24"/>
       <c r="AJ19" s="24"/>
@@ -22854,8 +22854,8 @@
       <c r="AN19" s="27">
         <v>13</v>
       </c>
-      <c r="AO19" s="287"/>
-      <c r="AQ19" s="288"/>
+      <c r="AO19" s="277"/>
+      <c r="AQ19" s="275"/>
     </row>
     <row r="20" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="16"/>
@@ -22866,13 +22866,13 @@
       <c r="G20" s="24"/>
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
-      <c r="K20" s="266"/>
-      <c r="L20" s="266"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
       <c r="M20" s="20"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="280"/>
-      <c r="P20" s="248"/>
-      <c r="Q20" s="265"/>
+      <c r="O20" s="266"/>
+      <c r="P20" s="260"/>
+      <c r="Q20" s="252"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="25"/>
@@ -22880,12 +22880,12 @@
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
-      <c r="Y20" s="265"/>
+      <c r="Y20" s="252"/>
       <c r="Z20" s="250"/>
-      <c r="AA20" s="263"/>
+      <c r="AA20" s="257"/>
       <c r="AB20" s="56"/>
-      <c r="AD20" s="266"/>
-      <c r="AE20" s="266"/>
+      <c r="AD20" s="258"/>
+      <c r="AE20" s="258"/>
       <c r="AF20" s="20"/>
       <c r="AG20" s="24"/>
       <c r="AJ20" s="24"/>
@@ -22895,7 +22895,7 @@
       <c r="AQ20" s="10"/>
     </row>
     <row r="21" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="283">
+      <c r="A21" s="255">
         <f>IF($AU$5=TRUE,A18+1,"")</f>
         <v>5</v>
       </c>
@@ -22914,15 +22914,15 @@
         <f>Games!L9</f>
         <v>0.36</v>
       </c>
-      <c r="F21" s="262" t="str">
+      <c r="F21" s="256" t="str">
         <f>Games!O9</f>
         <v>Campbell</v>
       </c>
-      <c r="G21" s="247" t="e" vm="74">
+      <c r="G21" s="259" t="e" vm="74">
         <f>_xlfn.XLOOKUP(F21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="264">
+      <c r="H21" s="251">
         <f>Games!L40</f>
         <v>0.33</v>
       </c>
@@ -22952,7 +22952,7 @@
         <v>59</v>
       </c>
       <c r="AG21" s="24"/>
-      <c r="AH21" s="264">
+      <c r="AH21" s="251">
         <f>Games!L48</f>
         <v>0.05</v>
       </c>
@@ -22960,7 +22960,7 @@
         <f>_xlfn.XLOOKUP(AJ21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ21" s="262" t="str">
+      <c r="AJ21" s="256" t="str">
         <f>Games!O25</f>
         <v>Appalachian State</v>
       </c>
@@ -22983,14 +22983,14 @@
       <c r="AQ21" s="9"/>
     </row>
     <row r="22" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="283"/>
+      <c r="A22" s="255"/>
       <c r="B22" s="28"/>
       <c r="C22" s="38"/>
       <c r="D22" s="71"/>
       <c r="E22" s="49"/>
-      <c r="F22" s="263"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="265"/>
+      <c r="F22" s="257"/>
+      <c r="G22" s="260"/>
+      <c r="H22" s="252"/>
       <c r="I22" s="24"/>
       <c r="J22" s="24"/>
       <c r="L22" s="25"/>
@@ -23011,17 +23011,17 @@
       <c r="AB22" s="56"/>
       <c r="AD22" s="29"/>
       <c r="AG22" s="24"/>
-      <c r="AH22" s="265"/>
+      <c r="AH22" s="252"/>
       <c r="AI22" s="250"/>
-      <c r="AJ22" s="263"/>
+      <c r="AJ22" s="257"/>
       <c r="AK22" s="55"/>
       <c r="AM22" s="39"/>
       <c r="AN22" s="28"/>
-      <c r="AO22" s="287">
+      <c r="AO22" s="277">
         <f>IF($AU$5=TRUE,AO18+1,"")</f>
         <v>21</v>
       </c>
-      <c r="AQ22" s="288"/>
+      <c r="AQ22" s="275"/>
     </row>
     <row r="23" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="16"/>
@@ -23040,21 +23040,21 @@
         <f>Games!N9</f>
         <v>0.64</v>
       </c>
-      <c r="F23" s="282">
+      <c r="F23" s="276">
         <f>IF($AU$5=TRUE,F15+1,"")</f>
         <v>35</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="49"/>
-      <c r="I23" s="279" t="str">
+      <c r="I23" s="265" t="str">
         <f>Games!O40</f>
         <v>Central Arkansas</v>
       </c>
-      <c r="J23" s="247" t="e" vm="76">
+      <c r="J23" s="259" t="e" vm="76">
         <f>_xlfn.XLOOKUP(I23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K23" s="264">
+      <c r="K23" s="251">
         <f>Games!L56</f>
         <v>0.91</v>
       </c>
@@ -23075,7 +23075,7 @@
       <c r="AA23" s="25"/>
       <c r="AB23" s="56"/>
       <c r="AD23" s="25"/>
-      <c r="AE23" s="264">
+      <c r="AE23" s="251">
         <f>Games!L60</f>
         <v>0.82</v>
       </c>
@@ -23083,13 +23083,13 @@
         <f>_xlfn.XLOOKUP(AG23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="262" t="str">
+      <c r="AG23" s="256" t="str">
         <f>Games!O48</f>
         <v>Arizona</v>
       </c>
       <c r="AH23" s="55"/>
       <c r="AI23" s="51"/>
-      <c r="AJ23" s="282">
+      <c r="AJ23" s="276">
         <f>IF($AU$5=TRUE,AJ15+1,"")</f>
         <v>43</v>
       </c>
@@ -23108,20 +23108,20 @@
       <c r="AN23" s="27">
         <v>11</v>
       </c>
-      <c r="AO23" s="287"/>
-      <c r="AQ23" s="288"/>
+      <c r="AO23" s="277"/>
+      <c r="AQ23" s="275"/>
     </row>
     <row r="24" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16"/>
       <c r="B24" s="28"/>
       <c r="C24" s="38"/>
       <c r="D24" s="71"/>
-      <c r="F24" s="283"/>
+      <c r="F24" s="255"/>
       <c r="G24" s="15"/>
       <c r="H24" s="50"/>
-      <c r="I24" s="280"/>
-      <c r="J24" s="248"/>
-      <c r="K24" s="265"/>
+      <c r="I24" s="266"/>
+      <c r="J24" s="260"/>
+      <c r="K24" s="252"/>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
       <c r="N24" s="50"/>
@@ -23139,15 +23139,15 @@
       <c r="AA24" s="25"/>
       <c r="AB24" s="56"/>
       <c r="AD24" s="25"/>
-      <c r="AE24" s="265"/>
+      <c r="AE24" s="252"/>
       <c r="AF24" s="250"/>
-      <c r="AG24" s="263"/>
+      <c r="AG24" s="257"/>
       <c r="AH24" s="56"/>
-      <c r="AJ24" s="283"/>
+      <c r="AJ24" s="255"/>
       <c r="AM24" s="39"/>
       <c r="AN24" s="28"/>
       <c r="AO24" s="17"/>
-      <c r="AQ24" s="288"/>
+      <c r="AQ24" s="275"/>
     </row>
     <row r="25" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16"/>
@@ -23166,15 +23166,15 @@
         <f>Games!L10</f>
         <v>0.04</v>
       </c>
-      <c r="F25" s="262" t="str">
+      <c r="F25" s="256" t="str">
         <f>Games!O10</f>
         <v>Central Arkansas</v>
       </c>
-      <c r="G25" s="247" t="e" vm="76">
+      <c r="G25" s="259" t="e" vm="76">
         <f>_xlfn.XLOOKUP(F25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H25" s="277">
+      <c r="H25" s="261">
         <f>Games!N40</f>
         <v>0.67</v>
       </c>
@@ -23200,7 +23200,7 @@
       <c r="AD25" s="25"/>
       <c r="AE25" s="55"/>
       <c r="AG25" s="24"/>
-      <c r="AH25" s="269">
+      <c r="AH25" s="253">
         <f>Games!N48</f>
         <v>0.95</v>
       </c>
@@ -23208,7 +23208,7 @@
         <f>_xlfn.XLOOKUP(AJ25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ25" s="262" t="str">
+      <c r="AJ25" s="256" t="str">
         <f>Games!O26</f>
         <v>Arizona</v>
       </c>
@@ -23228,10 +23228,10 @@
         <v>3</v>
       </c>
       <c r="AO25" s="17"/>
-      <c r="AQ25" s="288"/>
+      <c r="AQ25" s="275"/>
     </row>
     <row r="26" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="283">
+      <c r="A26" s="255">
         <f>IF($AU$5=TRUE,A21+1,"")</f>
         <v>6</v>
       </c>
@@ -23239,9 +23239,9 @@
       <c r="C26" s="38"/>
       <c r="D26" s="71"/>
       <c r="E26" s="49"/>
-      <c r="F26" s="263"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="278"/>
+      <c r="F26" s="257"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="262"/>
       <c r="I26" s="24"/>
       <c r="J26" s="24"/>
       <c r="K26" s="50"/>
@@ -23264,20 +23264,20 @@
       <c r="AD26" s="25"/>
       <c r="AE26" s="56"/>
       <c r="AG26" s="24"/>
-      <c r="AH26" s="270"/>
+      <c r="AH26" s="254"/>
       <c r="AI26" s="250"/>
-      <c r="AJ26" s="263"/>
+      <c r="AJ26" s="257"/>
       <c r="AK26" s="55"/>
       <c r="AM26" s="39"/>
       <c r="AN26" s="28"/>
-      <c r="AO26" s="287">
+      <c r="AO26" s="277">
         <f>IF($AU$5=TRUE,AO22+1,"")</f>
         <v>22</v>
       </c>
-      <c r="AQ26" s="288"/>
+      <c r="AQ26" s="275"/>
     </row>
     <row r="27" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="283"/>
+      <c r="A27" s="255"/>
       <c r="B27" s="27">
         <v>14</v>
       </c>
@@ -23295,38 +23295,38 @@
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
-      <c r="I27" s="283">
+      <c r="I27" s="255">
         <f>IF($AU$5=TRUE,I11+1,"")</f>
         <v>50</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="50"/>
-      <c r="L27" s="279" t="str">
+      <c r="L27" s="265" t="str">
         <f>Games!O56</f>
         <v>Central Arkansas</v>
       </c>
-      <c r="M27" s="247" t="e" vm="76">
+      <c r="M27" s="259" t="e" vm="76">
         <f>_xlfn.XLOOKUP(L27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N27" s="277">
+      <c r="N27" s="261">
         <f>Games!N64</f>
         <v>0.64</v>
       </c>
       <c r="O27" s="25"/>
       <c r="P27" s="25"/>
       <c r="Q27" s="50"/>
-      <c r="R27" s="279" t="str">
+      <c r="R27" s="265" t="str">
         <f>Games!O69</f>
         <v>Duke</v>
       </c>
-      <c r="S27" s="262"/>
-      <c r="T27" s="262"/>
-      <c r="U27" s="289" t="e" vm="92">
+      <c r="S27" s="256"/>
+      <c r="T27" s="256"/>
+      <c r="U27" s="271" t="e" vm="92">
         <f>_xlfn.XLOOKUP(R27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V27" s="267">
+      <c r="V27" s="273">
         <f>Games!L72</f>
         <v>0.59</v>
       </c>
@@ -23334,7 +23334,7 @@
       <c r="X27" s="25"/>
       <c r="Y27" s="56"/>
       <c r="AA27" s="25"/>
-      <c r="AB27" s="269">
+      <c r="AB27" s="253">
         <f>Games!N66</f>
         <v>0.23</v>
       </c>
@@ -23342,12 +23342,12 @@
         <f>_xlfn.XLOOKUP(AD27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD27" s="262" t="str">
+      <c r="AD27" s="256" t="str">
         <f>Games!O60</f>
         <v>Arizona</v>
       </c>
       <c r="AE27" s="56"/>
-      <c r="AG27" s="283">
+      <c r="AG27" s="255">
         <f>IF($AU$5=TRUE,AG11+1,"")</f>
         <v>54</v>
       </c>
@@ -23367,8 +23367,8 @@
       <c r="AN27" s="27">
         <v>14</v>
       </c>
-      <c r="AO27" s="287"/>
-      <c r="AQ27" s="288"/>
+      <c r="AO27" s="277"/>
+      <c r="AQ27" s="275"/>
     </row>
     <row r="28" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16"/>
@@ -23377,29 +23377,29 @@
       <c r="D28" s="71"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
-      <c r="I28" s="283"/>
+      <c r="I28" s="255"/>
       <c r="J28" s="15"/>
       <c r="K28" s="50"/>
-      <c r="L28" s="280"/>
-      <c r="M28" s="248"/>
-      <c r="N28" s="278"/>
+      <c r="L28" s="266"/>
+      <c r="M28" s="260"/>
+      <c r="N28" s="262"/>
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
       <c r="Q28" s="50"/>
-      <c r="R28" s="280"/>
-      <c r="S28" s="263"/>
-      <c r="T28" s="263"/>
-      <c r="U28" s="290"/>
-      <c r="V28" s="268"/>
+      <c r="R28" s="266"/>
+      <c r="S28" s="257"/>
+      <c r="T28" s="257"/>
+      <c r="U28" s="272"/>
+      <c r="V28" s="274"/>
       <c r="W28" s="24"/>
       <c r="X28" s="25"/>
       <c r="Y28" s="56"/>
       <c r="AA28" s="25"/>
-      <c r="AB28" s="270"/>
+      <c r="AB28" s="254"/>
       <c r="AC28" s="250"/>
-      <c r="AD28" s="263"/>
+      <c r="AD28" s="257"/>
       <c r="AE28" s="56"/>
-      <c r="AG28" s="283"/>
+      <c r="AG28" s="255"/>
       <c r="AJ28" s="24"/>
       <c r="AM28" s="39"/>
       <c r="AN28" s="28"/>
@@ -23422,15 +23422,15 @@
         <f>Games!L11</f>
         <v>0.42</v>
       </c>
-      <c r="F29" s="262" t="str">
+      <c r="F29" s="256" t="str">
         <f>Games!O11</f>
         <v>Central Michigan</v>
       </c>
-      <c r="G29" s="247" t="e" vm="78">
+      <c r="G29" s="259" t="e" vm="78">
         <f>_xlfn.XLOOKUP(F29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H29" s="264">
+      <c r="H29" s="251">
         <f>Games!L41</f>
         <v>0.57999999999999996</v>
       </c>
@@ -23454,7 +23454,7 @@
       <c r="AD29" s="25"/>
       <c r="AE29" s="56"/>
       <c r="AG29" s="24"/>
-      <c r="AH29" s="264">
+      <c r="AH29" s="251">
         <f>Games!L49</f>
         <v>0.96</v>
       </c>
@@ -23462,7 +23462,7 @@
         <f>_xlfn.XLOOKUP(AJ29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ29" s="262" t="str">
+      <c r="AJ29" s="256" t="str">
         <f>Games!O27</f>
         <v>Arkansas</v>
       </c>
@@ -23490,7 +23490,7 @@
       </c>
     </row>
     <row r="30" spans="1:43" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="283">
+      <c r="A30" s="255">
         <f>IF($AU$5=TRUE,A26+1,"")</f>
         <v>7</v>
       </c>
@@ -23498,9 +23498,9 @@
       <c r="C30" s="38"/>
       <c r="D30" s="71"/>
       <c r="E30" s="49"/>
-      <c r="F30" s="263"/>
-      <c r="G30" s="248"/>
-      <c r="H30" s="265"/>
+      <c r="F30" s="257"/>
+      <c r="G30" s="260"/>
+      <c r="H30" s="252"/>
       <c r="I30" s="24"/>
       <c r="J30" s="24"/>
       <c r="K30" s="50"/>
@@ -23521,19 +23521,19 @@
       <c r="AD30" s="25"/>
       <c r="AE30" s="56"/>
       <c r="AG30" s="24"/>
-      <c r="AH30" s="265"/>
+      <c r="AH30" s="252"/>
       <c r="AI30" s="250"/>
-      <c r="AJ30" s="263"/>
+      <c r="AJ30" s="257"/>
       <c r="AK30" s="55"/>
       <c r="AM30" s="39"/>
       <c r="AN30" s="28"/>
-      <c r="AO30" s="287">
+      <c r="AO30" s="277">
         <f>IF($AU$5=TRUE,AO26+1,"")</f>
         <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:43" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="283"/>
+      <c r="A31" s="255"/>
       <c r="B31" s="27">
         <v>10</v>
       </c>
@@ -23549,21 +23549,21 @@
         <f>Games!N11</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="F31" s="282">
+      <c r="F31" s="276">
         <f>IF($AU$5=TRUE,F23+1,"")</f>
         <v>36</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="49"/>
-      <c r="I31" s="279" t="str">
+      <c r="I31" s="265" t="str">
         <f>Games!O41</f>
         <v>Central Michigan</v>
       </c>
-      <c r="J31" s="247" t="e" vm="78">
+      <c r="J31" s="259" t="e" vm="78">
         <f>_xlfn.XLOOKUP(I31,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K31" s="277">
+      <c r="K31" s="261">
         <f>Games!N56</f>
         <v>0.09</v>
       </c>
@@ -23573,18 +23573,18 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="50"/>
       <c r="R31" s="4"/>
-      <c r="S31" s="255" t="s">
+      <c r="S31" s="286" t="s">
         <v>0</v>
       </c>
-      <c r="T31" s="255"/>
-      <c r="U31" s="255"/>
-      <c r="V31" s="255"/>
-      <c r="W31" s="255"/>
+      <c r="T31" s="286"/>
+      <c r="U31" s="286"/>
+      <c r="V31" s="286"/>
+      <c r="W31" s="286"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="56"/>
       <c r="AA31" s="25"/>
       <c r="AD31" s="25"/>
-      <c r="AE31" s="269">
+      <c r="AE31" s="253">
         <f>Games!N60</f>
         <v>0.18</v>
       </c>
@@ -23592,13 +23592,13 @@
         <f>_xlfn.XLOOKUP(AG31,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG31" s="262" t="str">
+      <c r="AG31" s="256" t="str">
         <f>Games!O49</f>
         <v>Arkansas</v>
       </c>
       <c r="AH31" s="55"/>
       <c r="AI31" s="51"/>
-      <c r="AJ31" s="282">
+      <c r="AJ31" s="276">
         <f>IF($AU$5=TRUE,AJ23+1,"")</f>
         <v>44</v>
       </c>
@@ -23617,42 +23617,42 @@
       <c r="AN31" s="27">
         <v>10</v>
       </c>
-      <c r="AO31" s="287"/>
+      <c r="AO31" s="277"/>
     </row>
     <row r="32" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16"/>
       <c r="B32" s="28"/>
       <c r="C32" s="38"/>
       <c r="D32" s="71"/>
-      <c r="F32" s="283"/>
+      <c r="F32" s="255"/>
       <c r="G32" s="15"/>
       <c r="H32" s="50"/>
-      <c r="I32" s="280"/>
-      <c r="J32" s="248"/>
-      <c r="K32" s="278"/>
+      <c r="I32" s="266"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="262"/>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
       <c r="O32" s="25"/>
       <c r="P32" s="25"/>
       <c r="Q32" s="50"/>
       <c r="R32" s="30"/>
-      <c r="S32" s="271" t="str">
+      <c r="S32" s="293" t="str">
         <f>Games!O72</f>
         <v>Duke</v>
       </c>
-      <c r="T32" s="272"/>
-      <c r="U32" s="272"/>
-      <c r="V32" s="272"/>
-      <c r="W32" s="273"/>
+      <c r="T32" s="294"/>
+      <c r="U32" s="294"/>
+      <c r="V32" s="294"/>
+      <c r="W32" s="295"/>
       <c r="X32" s="31"/>
       <c r="Y32" s="56"/>
       <c r="AA32" s="25"/>
       <c r="AD32" s="25"/>
-      <c r="AE32" s="270"/>
+      <c r="AE32" s="254"/>
       <c r="AF32" s="250"/>
-      <c r="AG32" s="263"/>
+      <c r="AG32" s="257"/>
       <c r="AH32" s="56"/>
-      <c r="AJ32" s="283"/>
+      <c r="AJ32" s="255"/>
       <c r="AM32" s="39"/>
       <c r="AN32" s="28"/>
       <c r="AO32" s="17"/>
@@ -23674,15 +23674,15 @@
         <f>Games!L12</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="F33" s="262" t="str">
+      <c r="F33" s="256" t="str">
         <f>Games!O12</f>
         <v>Charleston Southern</v>
       </c>
-      <c r="G33" s="247" t="e" vm="79">
+      <c r="G33" s="259" t="e" vm="79">
         <f>_xlfn.XLOOKUP(F33,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H33" s="277">
+      <c r="H33" s="261">
         <f>Games!N41</f>
         <v>0.42</v>
       </c>
@@ -23694,17 +23694,17 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="50"/>
       <c r="R33" s="30"/>
-      <c r="S33" s="274"/>
-      <c r="T33" s="275"/>
-      <c r="U33" s="275"/>
-      <c r="V33" s="275"/>
-      <c r="W33" s="276"/>
+      <c r="S33" s="296"/>
+      <c r="T33" s="297"/>
+      <c r="U33" s="297"/>
+      <c r="V33" s="297"/>
+      <c r="W33" s="298"/>
       <c r="X33" s="31"/>
       <c r="Y33" s="56"/>
       <c r="AA33" s="25"/>
       <c r="AD33" s="25"/>
       <c r="AG33" s="24"/>
-      <c r="AH33" s="269">
+      <c r="AH33" s="253">
         <f>Games!N49</f>
         <v>0.04</v>
       </c>
@@ -23712,7 +23712,7 @@
         <f>_xlfn.XLOOKUP(AJ33,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ33" s="262" t="str">
+      <c r="AJ33" s="256" t="str">
         <f>Games!O28</f>
         <v>Arkansas-Pine Bluff</v>
       </c>
@@ -23735,7 +23735,7 @@
       <c r="AQ33" s="9"/>
     </row>
     <row r="34" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="283">
+      <c r="A34" s="255">
         <f>IF($AU$5=TRUE,A30+1,"")</f>
         <v>8</v>
       </c>
@@ -23743,9 +23743,9 @@
       <c r="C34" s="38"/>
       <c r="D34" s="71"/>
       <c r="E34" s="49"/>
-      <c r="F34" s="263"/>
-      <c r="G34" s="248"/>
-      <c r="H34" s="278"/>
+      <c r="F34" s="257"/>
+      <c r="G34" s="260"/>
+      <c r="H34" s="262"/>
       <c r="I34" s="24"/>
       <c r="J34" s="24"/>
       <c r="L34" s="25"/>
@@ -23764,20 +23764,20 @@
       <c r="AA34" s="25"/>
       <c r="AD34" s="25"/>
       <c r="AG34" s="24"/>
-      <c r="AH34" s="270"/>
+      <c r="AH34" s="254"/>
       <c r="AI34" s="250"/>
-      <c r="AJ34" s="263"/>
+      <c r="AJ34" s="257"/>
       <c r="AK34" s="55"/>
       <c r="AM34" s="39"/>
       <c r="AN34" s="28"/>
-      <c r="AO34" s="287">
+      <c r="AO34" s="277">
         <f>IF($AU$5=TRUE,AO30+1,"")</f>
         <v>24</v>
       </c>
-      <c r="AQ34" s="288"/>
+      <c r="AQ34" s="275"/>
     </row>
     <row r="35" spans="1:43" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="283"/>
+      <c r="A35" s="255"/>
       <c r="B35" s="27">
         <v>15</v>
       </c>
@@ -23807,12 +23807,12 @@
       <c r="Q35" s="50"/>
       <c r="R35" s="25"/>
       <c r="S35" s="25"/>
-      <c r="T35" s="283">
+      <c r="T35" s="255">
         <f>IF($AU$5=TRUE,AA35+1,"")</f>
         <v>63</v>
       </c>
-      <c r="U35" s="283"/>
-      <c r="V35" s="283"/>
+      <c r="U35" s="255"/>
+      <c r="V35" s="255"/>
       <c r="W35" s="25"/>
       <c r="X35" s="25"/>
       <c r="Y35" s="56"/>
@@ -23838,8 +23838,8 @@
       <c r="AN35" s="27">
         <v>15</v>
       </c>
-      <c r="AO35" s="287"/>
-      <c r="AQ35" s="288"/>
+      <c r="AO35" s="277"/>
+      <c r="AQ35" s="275"/>
     </row>
     <row r="36" spans="1:43" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
@@ -23870,7 +23870,7 @@
       <c r="AM36" s="39"/>
       <c r="AN36" s="28"/>
       <c r="AO36" s="17"/>
-      <c r="AQ36" s="288"/>
+      <c r="AQ36" s="275"/>
     </row>
     <row r="37" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16"/>
@@ -23889,15 +23889,15 @@
         <f>Games!L13</f>
         <v>0.46</v>
       </c>
-      <c r="F37" s="262" t="str">
+      <c r="F37" s="256" t="str">
         <f>Games!O13</f>
         <v>Austin Peay</v>
       </c>
-      <c r="G37" s="247" t="e" vm="82">
+      <c r="G37" s="259" t="e" vm="82">
         <f>_xlfn.XLOOKUP(F37,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H37" s="264">
+      <c r="H37" s="251">
         <f>Games!L42</f>
         <v>0.42</v>
       </c>
@@ -23919,7 +23919,7 @@
       <c r="AA37" s="25"/>
       <c r="AD37" s="25"/>
       <c r="AG37" s="24"/>
-      <c r="AH37" s="264">
+      <c r="AH37" s="251">
         <f>Games!L50</f>
         <v>0.85</v>
       </c>
@@ -23927,7 +23927,7 @@
         <f>_xlfn.XLOOKUP(AJ37,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ37" s="262" t="str">
+      <c r="AJ37" s="256" t="str">
         <f>Games!O29</f>
         <v>Chattanooga</v>
       </c>
@@ -23947,10 +23947,10 @@
         <v>1</v>
       </c>
       <c r="AO37" s="17"/>
-      <c r="AQ37" s="288"/>
+      <c r="AQ37" s="275"/>
     </row>
     <row r="38" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="283">
+      <c r="A38" s="255">
         <f>IF($AU$5=TRUE,A34+1,"")</f>
         <v>9</v>
       </c>
@@ -23958,9 +23958,9 @@
       <c r="C38" s="38"/>
       <c r="D38" s="71"/>
       <c r="E38" s="49"/>
-      <c r="F38" s="263"/>
-      <c r="G38" s="248"/>
-      <c r="H38" s="265"/>
+      <c r="F38" s="257"/>
+      <c r="G38" s="260"/>
+      <c r="H38" s="252"/>
       <c r="I38" s="24"/>
       <c r="J38" s="24"/>
       <c r="L38" s="25"/>
@@ -23979,19 +23979,19 @@
       <c r="AA38" s="25"/>
       <c r="AD38" s="25"/>
       <c r="AG38" s="24"/>
-      <c r="AH38" s="265"/>
+      <c r="AH38" s="252"/>
       <c r="AI38" s="250"/>
-      <c r="AJ38" s="263"/>
+      <c r="AJ38" s="257"/>
       <c r="AK38" s="55"/>
       <c r="AM38" s="39"/>
       <c r="AN38" s="28"/>
-      <c r="AO38" s="287">
+      <c r="AO38" s="277">
         <f>IF($AU$5=TRUE,AO34+1,"")</f>
         <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="283"/>
+      <c r="A39" s="255"/>
       <c r="B39" s="27">
         <v>16</v>
       </c>
@@ -24007,21 +24007,21 @@
         <f>Games!N13</f>
         <v>0.54</v>
       </c>
-      <c r="F39" s="282">
+      <c r="F39" s="276">
         <f>IF($AU$5=TRUE,F31+1,"")</f>
         <v>37</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="49"/>
-      <c r="I39" s="279" t="str">
+      <c r="I39" s="265" t="str">
         <f>Games!O42</f>
         <v>Baylor</v>
       </c>
-      <c r="J39" s="247" t="e" vm="84">
+      <c r="J39" s="259" t="e" vm="84">
         <f>_xlfn.XLOOKUP(I39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K39" s="264">
+      <c r="K39" s="251">
         <f>Games!L57</f>
         <v>0.59</v>
       </c>
@@ -24032,24 +24032,24 @@
       <c r="Q39" s="50"/>
       <c r="R39" s="25"/>
       <c r="S39" s="25"/>
-      <c r="T39" s="267">
+      <c r="T39" s="273">
         <f>Games!N72</f>
         <v>0.41</v>
       </c>
-      <c r="U39" s="293" t="e" vm="100">
+      <c r="U39" s="267" t="e" vm="100">
         <f>_xlfn.XLOOKUP(V39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V39" s="262" t="str">
+      <c r="V39" s="256" t="str">
         <f>Games!O70</f>
         <v>Alabama</v>
       </c>
-      <c r="W39" s="262"/>
-      <c r="X39" s="295"/>
+      <c r="W39" s="256"/>
+      <c r="X39" s="269"/>
       <c r="Y39" s="56"/>
       <c r="AA39" s="25"/>
       <c r="AD39" s="25"/>
-      <c r="AE39" s="269">
+      <c r="AE39" s="253">
         <f>Games!L61</f>
         <v>0.87</v>
       </c>
@@ -24057,13 +24057,13 @@
         <f>_xlfn.XLOOKUP(AG39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG39" s="262" t="str">
+      <c r="AG39" s="256" t="str">
         <f>Games!O50</f>
         <v>Chattanooga</v>
       </c>
       <c r="AH39" s="55"/>
       <c r="AI39" s="51"/>
-      <c r="AJ39" s="282">
+      <c r="AJ39" s="276">
         <f>IF($AU$5=TRUE,AJ31+1,"")</f>
         <v>45</v>
       </c>
@@ -24082,19 +24082,19 @@
       <c r="AN39" s="27">
         <v>16</v>
       </c>
-      <c r="AO39" s="287"/>
+      <c r="AO39" s="277"/>
     </row>
     <row r="40" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16"/>
       <c r="B40" s="28"/>
       <c r="C40" s="38"/>
       <c r="D40" s="71"/>
-      <c r="F40" s="283"/>
+      <c r="F40" s="255"/>
       <c r="G40" s="15"/>
       <c r="H40" s="50"/>
-      <c r="I40" s="280"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="265"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="252"/>
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="O40" s="25"/>
@@ -24102,19 +24102,19 @@
       <c r="Q40" s="50"/>
       <c r="R40" s="25"/>
       <c r="S40" s="25"/>
-      <c r="T40" s="268"/>
-      <c r="U40" s="294"/>
-      <c r="V40" s="263"/>
-      <c r="W40" s="263"/>
-      <c r="X40" s="296"/>
+      <c r="T40" s="274"/>
+      <c r="U40" s="268"/>
+      <c r="V40" s="257"/>
+      <c r="W40" s="257"/>
+      <c r="X40" s="270"/>
       <c r="Y40" s="56"/>
       <c r="AA40" s="25"/>
       <c r="AD40" s="25"/>
-      <c r="AE40" s="270"/>
+      <c r="AE40" s="254"/>
       <c r="AF40" s="250"/>
-      <c r="AG40" s="263"/>
+      <c r="AG40" s="257"/>
       <c r="AH40" s="56"/>
-      <c r="AJ40" s="283"/>
+      <c r="AJ40" s="255"/>
       <c r="AM40" s="39"/>
       <c r="AN40" s="28"/>
       <c r="AO40" s="17"/>
@@ -24136,15 +24136,15 @@
         <f>Games!L14</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F41" s="262" t="str">
+      <c r="F41" s="256" t="str">
         <f>Games!O14</f>
         <v>Baylor</v>
       </c>
-      <c r="G41" s="247" t="e" vm="84">
+      <c r="G41" s="259" t="e" vm="84">
         <f>_xlfn.XLOOKUP(F41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H41" s="277">
+      <c r="H41" s="261">
         <f>Games!N42</f>
         <v>0.57999999999999996</v>
       </c>
@@ -24168,7 +24168,7 @@
       <c r="AD41" s="25"/>
       <c r="AE41" s="55"/>
       <c r="AG41" s="24"/>
-      <c r="AH41" s="269">
+      <c r="AH41" s="253">
         <f>Games!N50</f>
         <v>0.15</v>
       </c>
@@ -24176,7 +24176,7 @@
         <f>_xlfn.XLOOKUP(AJ41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ41" s="262" t="str">
+      <c r="AJ41" s="256" t="str">
         <f>Games!O30</f>
         <v>Clemson</v>
       </c>
@@ -24198,7 +24198,7 @@
       <c r="AO41" s="17"/>
     </row>
     <row r="42" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="283">
+      <c r="A42" s="255">
         <f>IF($AU$5=TRUE,A38+1,"")</f>
         <v>10</v>
       </c>
@@ -24206,9 +24206,9 @@
       <c r="C42" s="38"/>
       <c r="D42" s="71"/>
       <c r="E42" s="49"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="248"/>
-      <c r="H42" s="278"/>
+      <c r="F42" s="257"/>
+      <c r="G42" s="260"/>
+      <c r="H42" s="262"/>
       <c r="I42" s="24"/>
       <c r="J42" s="24"/>
       <c r="K42" s="50"/>
@@ -24229,19 +24229,19 @@
       <c r="AD42" s="25"/>
       <c r="AE42" s="56"/>
       <c r="AG42" s="24"/>
-      <c r="AH42" s="270"/>
+      <c r="AH42" s="254"/>
       <c r="AI42" s="250"/>
-      <c r="AJ42" s="263"/>
+      <c r="AJ42" s="257"/>
       <c r="AK42" s="55"/>
       <c r="AM42" s="39"/>
       <c r="AN42" s="28"/>
-      <c r="AO42" s="287">
+      <c r="AO42" s="277">
         <f>IF($AU$5=TRUE,AO38+1,"")</f>
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="283"/>
+      <c r="A43" s="255"/>
       <c r="B43" s="27">
         <v>9</v>
       </c>
@@ -24259,21 +24259,21 @@
       </c>
       <c r="F43" s="24"/>
       <c r="G43" s="24"/>
-      <c r="I43" s="283">
+      <c r="I43" s="255">
         <f>IF($AU$5=TRUE,I27+1,"")</f>
         <v>51</v>
       </c>
       <c r="J43" s="15"/>
       <c r="K43" s="50"/>
-      <c r="L43" s="279" t="str">
+      <c r="L43" s="265" t="str">
         <f>Games!O57</f>
         <v>Baylor</v>
       </c>
-      <c r="M43" s="247" t="e" vm="84">
+      <c r="M43" s="259" t="e" vm="84">
         <f>_xlfn.XLOOKUP(L43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N43" s="264">
+      <c r="N43" s="251">
         <f>Games!L65</f>
         <v>0.15</v>
       </c>
@@ -24289,7 +24289,7 @@
       <c r="X43" s="25"/>
       <c r="Y43" s="56"/>
       <c r="AA43" s="25"/>
-      <c r="AB43" s="264">
+      <c r="AB43" s="251">
         <f>Games!L67</f>
         <v>0.03</v>
       </c>
@@ -24297,12 +24297,12 @@
         <f>_xlfn.XLOOKUP(AD43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD43" s="291" t="str">
+      <c r="AD43" s="263" t="str">
         <f>Games!O61</f>
         <v>Chattanooga</v>
       </c>
       <c r="AE43" s="56"/>
-      <c r="AG43" s="283">
+      <c r="AG43" s="255">
         <f>IF($AU$5=TRUE,AG27+1,"")</f>
         <v>55</v>
       </c>
@@ -24322,7 +24322,7 @@
       <c r="AN43" s="27">
         <v>9</v>
       </c>
-      <c r="AO43" s="287"/>
+      <c r="AO43" s="277"/>
     </row>
     <row r="44" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16"/>
@@ -24331,12 +24331,12 @@
       <c r="D44" s="71"/>
       <c r="F44" s="24"/>
       <c r="G44" s="24"/>
-      <c r="I44" s="283"/>
+      <c r="I44" s="255"/>
       <c r="J44" s="15"/>
       <c r="K44" s="50"/>
-      <c r="L44" s="280"/>
-      <c r="M44" s="248"/>
-      <c r="N44" s="265"/>
+      <c r="L44" s="266"/>
+      <c r="M44" s="260"/>
+      <c r="N44" s="252"/>
       <c r="O44" s="25"/>
       <c r="P44" s="25"/>
       <c r="Q44" s="50"/>
@@ -24349,11 +24349,11 @@
       <c r="X44" s="25"/>
       <c r="Y44" s="56"/>
       <c r="AA44" s="25"/>
-      <c r="AB44" s="265"/>
+      <c r="AB44" s="252"/>
       <c r="AC44" s="250"/>
-      <c r="AD44" s="292"/>
+      <c r="AD44" s="264"/>
       <c r="AE44" s="56"/>
-      <c r="AG44" s="283"/>
+      <c r="AG44" s="255"/>
       <c r="AJ44" s="24"/>
       <c r="AM44" s="39"/>
       <c r="AN44" s="28"/>
@@ -24376,15 +24376,15 @@
         <f>Games!L15</f>
         <v>0.16</v>
       </c>
-      <c r="F45" s="262" t="str">
+      <c r="F45" s="256" t="str">
         <f>Games!O15</f>
         <v>Belmont</v>
       </c>
-      <c r="G45" s="247" t="e" vm="86">
+      <c r="G45" s="259" t="e" vm="86">
         <f>_xlfn.XLOOKUP(F45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H45" s="264">
+      <c r="H45" s="251">
         <f>Games!L43</f>
         <v>0.62</v>
       </c>
@@ -24410,7 +24410,7 @@
       <c r="AD45" s="25"/>
       <c r="AE45" s="56"/>
       <c r="AG45" s="24"/>
-      <c r="AH45" s="264">
+      <c r="AH45" s="251">
         <f>Games!L51</f>
         <v>0.71</v>
       </c>
@@ -24418,7 +24418,7 @@
         <f>_xlfn.XLOOKUP(AJ45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ45" s="262" t="str">
+      <c r="AJ45" s="256" t="str">
         <f>Games!O31</f>
         <v>Coastal Carolina</v>
       </c>
@@ -24440,7 +24440,7 @@
       <c r="AO45" s="17"/>
     </row>
     <row r="46" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="283">
+      <c r="A46" s="255">
         <f>IF($AU$5=TRUE,A42+1,"")</f>
         <v>11</v>
       </c>
@@ -24448,9 +24448,9 @@
       <c r="C46" s="38"/>
       <c r="D46" s="71"/>
       <c r="E46" s="49"/>
-      <c r="F46" s="263"/>
-      <c r="G46" s="248"/>
-      <c r="H46" s="265"/>
+      <c r="F46" s="257"/>
+      <c r="G46" s="260"/>
+      <c r="H46" s="252"/>
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
       <c r="K46" s="50"/>
@@ -24473,19 +24473,19 @@
       <c r="AD46" s="25"/>
       <c r="AE46" s="56"/>
       <c r="AG46" s="24"/>
-      <c r="AH46" s="265"/>
+      <c r="AH46" s="252"/>
       <c r="AI46" s="250"/>
-      <c r="AJ46" s="263"/>
+      <c r="AJ46" s="257"/>
       <c r="AK46" s="55"/>
       <c r="AM46" s="39"/>
       <c r="AN46" s="28"/>
-      <c r="AO46" s="287">
+      <c r="AO46" s="277">
         <f>IF($AU$5=TRUE,AO42+1,"")</f>
         <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="283"/>
+      <c r="A47" s="255"/>
       <c r="B47" s="27">
         <v>12</v>
       </c>
@@ -24501,21 +24501,21 @@
         <f>Games!N15</f>
         <v>0.84</v>
       </c>
-      <c r="F47" s="282">
+      <c r="F47" s="276">
         <f>IF($AU$5=TRUE,F39+1,"")</f>
         <v>38</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="49"/>
-      <c r="I47" s="279" t="str">
+      <c r="I47" s="265" t="str">
         <f>Games!O43</f>
         <v>Belmont</v>
       </c>
-      <c r="J47" s="247" t="e" vm="86">
+      <c r="J47" s="259" t="e" vm="86">
         <f>_xlfn.XLOOKUP(I47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K47" s="277">
+      <c r="K47" s="261">
         <f>Games!N57</f>
         <v>0.41</v>
       </c>
@@ -24536,7 +24536,7 @@
       <c r="AA47" s="25"/>
       <c r="AB47" s="56"/>
       <c r="AD47" s="25"/>
-      <c r="AE47" s="269">
+      <c r="AE47" s="253">
         <f>Games!N61</f>
         <v>0.13</v>
       </c>
@@ -24544,13 +24544,13 @@
         <f>_xlfn.XLOOKUP(AG47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG47" s="262" t="str">
+      <c r="AG47" s="256" t="str">
         <f>Games!O51</f>
         <v>Coastal Carolina</v>
       </c>
       <c r="AH47" s="55"/>
       <c r="AI47" s="51"/>
-      <c r="AJ47" s="282">
+      <c r="AJ47" s="276">
         <f>IF($AU$5=TRUE,AJ39+1,"")</f>
         <v>46</v>
       </c>
@@ -24569,19 +24569,19 @@
       <c r="AN47" s="27">
         <v>12</v>
       </c>
-      <c r="AO47" s="287"/>
+      <c r="AO47" s="277"/>
     </row>
     <row r="48" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16"/>
       <c r="B48" s="28"/>
       <c r="C48" s="38"/>
       <c r="D48" s="71"/>
-      <c r="F48" s="283"/>
+      <c r="F48" s="255"/>
       <c r="G48" s="15"/>
       <c r="H48" s="50"/>
-      <c r="I48" s="280"/>
-      <c r="J48" s="248"/>
-      <c r="K48" s="278"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="260"/>
+      <c r="K48" s="262"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
       <c r="N48" s="50"/>
@@ -24599,11 +24599,11 @@
       <c r="AA48" s="25"/>
       <c r="AB48" s="56"/>
       <c r="AD48" s="25"/>
-      <c r="AE48" s="270"/>
+      <c r="AE48" s="254"/>
       <c r="AF48" s="250"/>
-      <c r="AG48" s="263"/>
+      <c r="AG48" s="257"/>
       <c r="AH48" s="56"/>
-      <c r="AJ48" s="283"/>
+      <c r="AJ48" s="255"/>
       <c r="AM48" s="39"/>
       <c r="AN48" s="28"/>
       <c r="AO48" s="17"/>
@@ -24625,15 +24625,15 @@
         <f>Games!L16</f>
         <v>0.83</v>
       </c>
-      <c r="F49" s="262" t="str">
+      <c r="F49" s="256" t="str">
         <f>Games!O16</f>
         <v>Bethune-Cookman</v>
       </c>
-      <c r="G49" s="247" t="e" vm="87">
+      <c r="G49" s="259" t="e" vm="87">
         <f>_xlfn.XLOOKUP(F49,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H49" s="277">
+      <c r="H49" s="261">
         <f>Games!N43</f>
         <v>0.38</v>
       </c>
@@ -24657,7 +24657,7 @@
       <c r="AB49" s="56"/>
       <c r="AD49" s="25"/>
       <c r="AG49" s="24"/>
-      <c r="AH49" s="269">
+      <c r="AH49" s="253">
         <f>Games!N51</f>
         <v>0.28999999999999998</v>
       </c>
@@ -24665,7 +24665,7 @@
         <f>_xlfn.XLOOKUP(AJ49,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ49" s="262" t="str">
+      <c r="AJ49" s="256" t="str">
         <f>Games!O32</f>
         <v>Colgate</v>
       </c>
@@ -24687,7 +24687,7 @@
       <c r="AO49" s="17"/>
     </row>
     <row r="50" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="283">
+      <c r="A50" s="255">
         <f>IF($AU$5=TRUE,A46+1,"")</f>
         <v>12</v>
       </c>
@@ -24695,9 +24695,9 @@
       <c r="C50" s="38"/>
       <c r="D50" s="71"/>
       <c r="E50" s="49"/>
-      <c r="F50" s="263"/>
-      <c r="G50" s="248"/>
-      <c r="H50" s="278"/>
+      <c r="F50" s="257"/>
+      <c r="G50" s="260"/>
+      <c r="H50" s="262"/>
       <c r="I50" s="24"/>
       <c r="J50" s="24"/>
       <c r="L50" s="25"/>
@@ -24718,19 +24718,19 @@
       <c r="AB50" s="56"/>
       <c r="AD50" s="25"/>
       <c r="AG50" s="24"/>
-      <c r="AH50" s="270"/>
+      <c r="AH50" s="254"/>
       <c r="AI50" s="250"/>
-      <c r="AJ50" s="263"/>
+      <c r="AJ50" s="257"/>
       <c r="AK50" s="55"/>
       <c r="AM50" s="39"/>
       <c r="AN50" s="28"/>
-      <c r="AO50" s="287">
+      <c r="AO50" s="277">
         <f>IF($AU$5=TRUE,AO46+1,"")</f>
         <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="283"/>
+      <c r="A51" s="255"/>
       <c r="B51" s="27">
         <v>13</v>
       </c>
@@ -24750,21 +24750,21 @@
       <c r="G51" s="24"/>
       <c r="I51" s="24"/>
       <c r="J51" s="24"/>
-      <c r="K51" s="266" t="s">
+      <c r="K51" s="258" t="s">
         <v>4</v>
       </c>
-      <c r="L51" s="266"/>
+      <c r="L51" s="258"/>
       <c r="M51" s="20"/>
       <c r="N51" s="50"/>
-      <c r="O51" s="279" t="str">
+      <c r="O51" s="265" t="str">
         <f>Games!O65</f>
         <v>Duke</v>
       </c>
-      <c r="P51" s="247" t="e" vm="92">
+      <c r="P51" s="259" t="e" vm="92">
         <f>_xlfn.XLOOKUP(O51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q51" s="277">
+      <c r="Q51" s="261">
         <f>Games!N69</f>
         <v>0.79</v>
       </c>
@@ -24775,7 +24775,7 @@
       <c r="V51" s="25"/>
       <c r="W51" s="25"/>
       <c r="X51" s="25"/>
-      <c r="Y51" s="269">
+      <c r="Y51" s="253">
         <f>Games!N70</f>
         <v>0.32</v>
       </c>
@@ -24783,15 +24783,15 @@
         <f>_xlfn.XLOOKUP(AA51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA51" s="262" t="str">
+      <c r="AA51" s="256" t="str">
         <f>Games!O67</f>
         <v>Connecticut</v>
       </c>
       <c r="AB51" s="56"/>
-      <c r="AD51" s="266" t="s">
+      <c r="AD51" s="258" t="s">
         <v>14</v>
       </c>
-      <c r="AE51" s="266"/>
+      <c r="AE51" s="258"/>
       <c r="AF51" s="20"/>
       <c r="AG51" s="24"/>
       <c r="AJ51" s="24"/>
@@ -24810,7 +24810,7 @@
       <c r="AN51" s="27">
         <v>13</v>
       </c>
-      <c r="AO51" s="287"/>
+      <c r="AO51" s="277"/>
     </row>
     <row r="52" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="16"/>
@@ -24821,13 +24821,13 @@
       <c r="G52" s="24"/>
       <c r="I52" s="24"/>
       <c r="J52" s="24"/>
-      <c r="K52" s="266"/>
-      <c r="L52" s="266"/>
+      <c r="K52" s="258"/>
+      <c r="L52" s="258"/>
       <c r="M52" s="20"/>
       <c r="N52" s="50"/>
-      <c r="O52" s="280"/>
-      <c r="P52" s="248"/>
-      <c r="Q52" s="278"/>
+      <c r="O52" s="266"/>
+      <c r="P52" s="260"/>
+      <c r="Q52" s="262"/>
       <c r="R52" s="25"/>
       <c r="S52" s="25"/>
       <c r="T52" s="25"/>
@@ -24835,12 +24835,12 @@
       <c r="V52" s="25"/>
       <c r="W52" s="25"/>
       <c r="X52" s="25"/>
-      <c r="Y52" s="270"/>
+      <c r="Y52" s="254"/>
       <c r="Z52" s="250"/>
-      <c r="AA52" s="263"/>
+      <c r="AA52" s="257"/>
       <c r="AB52" s="56"/>
-      <c r="AD52" s="266"/>
-      <c r="AE52" s="266"/>
+      <c r="AD52" s="258"/>
+      <c r="AE52" s="258"/>
       <c r="AF52" s="20"/>
       <c r="AG52" s="24"/>
       <c r="AJ52" s="24"/>
@@ -24865,15 +24865,15 @@
         <f>Games!L17</f>
         <v>0.82</v>
       </c>
-      <c r="F53" s="262" t="str">
+      <c r="F53" s="256" t="str">
         <f>Games!O17</f>
         <v>Boise State</v>
       </c>
-      <c r="G53" s="247" t="e" vm="89">
+      <c r="G53" s="259" t="e" vm="89">
         <f>_xlfn.XLOOKUP(F53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H53" s="264">
+      <c r="H53" s="251">
         <f>Games!L44</f>
         <v>7.0000000000000007E-2</v>
       </c>
@@ -24902,7 +24902,7 @@
         <v>60</v>
       </c>
       <c r="AG53" s="24"/>
-      <c r="AH53" s="264">
+      <c r="AH53" s="251">
         <f>Games!L52</f>
         <v>0.18</v>
       </c>
@@ -24910,7 +24910,7 @@
         <f>_xlfn.XLOOKUP(AJ53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ53" s="262" t="str">
+      <c r="AJ53" s="256" t="str">
         <f>Games!O33</f>
         <v>Colorado</v>
       </c>
@@ -24932,7 +24932,7 @@
       <c r="AO53" s="17"/>
     </row>
     <row r="54" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="283">
+      <c r="A54" s="255">
         <f>IF($AU$5=TRUE,A50+1,"")</f>
         <v>13</v>
       </c>
@@ -24940,9 +24940,9 @@
       <c r="C54" s="38"/>
       <c r="D54" s="71"/>
       <c r="E54" s="49"/>
-      <c r="F54" s="263"/>
-      <c r="G54" s="248"/>
-      <c r="H54" s="265"/>
+      <c r="F54" s="257"/>
+      <c r="G54" s="260"/>
+      <c r="H54" s="252"/>
       <c r="I54" s="24"/>
       <c r="J54" s="24"/>
       <c r="L54" s="25"/>
@@ -24961,19 +24961,19 @@
       <c r="AB54" s="56"/>
       <c r="AD54" s="25"/>
       <c r="AG54" s="24"/>
-      <c r="AH54" s="265"/>
+      <c r="AH54" s="252"/>
       <c r="AI54" s="250"/>
-      <c r="AJ54" s="263"/>
+      <c r="AJ54" s="257"/>
       <c r="AK54" s="55"/>
       <c r="AM54" s="39"/>
       <c r="AN54" s="28"/>
-      <c r="AO54" s="287">
+      <c r="AO54" s="277">
         <f>IF($AU$5=TRUE,AO50+1,"")</f>
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="283"/>
+      <c r="A55" s="255"/>
       <c r="B55" s="27">
         <v>11</v>
       </c>
@@ -24989,21 +24989,21 @@
         <f>Games!N17</f>
         <v>0.18</v>
       </c>
-      <c r="F55" s="282">
+      <c r="F55" s="276">
         <f>IF($AU$5=TRUE,F47+1,"")</f>
         <v>39</v>
       </c>
       <c r="G55" s="14"/>
       <c r="H55" s="49"/>
-      <c r="I55" s="279" t="str">
+      <c r="I55" s="265" t="str">
         <f>Games!O44</f>
         <v>Duke</v>
       </c>
-      <c r="J55" s="247" t="e" vm="92">
+      <c r="J55" s="259" t="e" vm="92">
         <f>_xlfn.XLOOKUP(I55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K55" s="264">
+      <c r="K55" s="251">
         <f>Games!L58</f>
         <v>0.71</v>
       </c>
@@ -25022,7 +25022,7 @@
       <c r="AA55" s="25"/>
       <c r="AB55" s="56"/>
       <c r="AD55" s="25"/>
-      <c r="AE55" s="264">
+      <c r="AE55" s="251">
         <f>Games!L62</f>
         <v>0.87</v>
       </c>
@@ -25030,13 +25030,13 @@
         <f>_xlfn.XLOOKUP(AG55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG55" s="262" t="str">
+      <c r="AG55" s="256" t="str">
         <f>Games!O52</f>
         <v>Connecticut</v>
       </c>
       <c r="AH55" s="55"/>
       <c r="AI55" s="51"/>
-      <c r="AJ55" s="282">
+      <c r="AJ55" s="276">
         <f>IF($AU$5=TRUE,AJ47+1,"")</f>
         <v>47</v>
       </c>
@@ -25055,19 +25055,19 @@
       <c r="AN55" s="32">
         <v>11</v>
       </c>
-      <c r="AO55" s="287"/>
+      <c r="AO55" s="277"/>
     </row>
     <row r="56" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="16"/>
       <c r="B56" s="28"/>
       <c r="C56" s="38"/>
       <c r="D56" s="71"/>
-      <c r="F56" s="283"/>
+      <c r="F56" s="255"/>
       <c r="G56" s="15"/>
       <c r="H56" s="50"/>
-      <c r="I56" s="280"/>
-      <c r="J56" s="248"/>
-      <c r="K56" s="265"/>
+      <c r="I56" s="266"/>
+      <c r="J56" s="260"/>
+      <c r="K56" s="252"/>
       <c r="L56" s="25"/>
       <c r="M56" s="25"/>
       <c r="N56" s="50"/>
@@ -25083,11 +25083,11 @@
       <c r="AA56" s="25"/>
       <c r="AB56" s="56"/>
       <c r="AD56" s="25"/>
-      <c r="AE56" s="265"/>
+      <c r="AE56" s="252"/>
       <c r="AF56" s="250"/>
-      <c r="AG56" s="263"/>
+      <c r="AG56" s="257"/>
       <c r="AH56" s="56"/>
-      <c r="AJ56" s="283"/>
+      <c r="AJ56" s="255"/>
       <c r="AM56" s="39"/>
       <c r="AN56" s="28"/>
       <c r="AO56" s="17"/>
@@ -25109,15 +25109,15 @@
         <f>Games!L18</f>
         <v>0.01</v>
       </c>
-      <c r="F57" s="262" t="str">
+      <c r="F57" s="256" t="str">
         <f>Games!O18</f>
         <v>Duke</v>
       </c>
-      <c r="G57" s="247" t="e" vm="92">
+      <c r="G57" s="259" t="e" vm="92">
         <f>_xlfn.XLOOKUP(F57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H57" s="277">
+      <c r="H57" s="261">
         <f>Games!N44</f>
         <v>0.93</v>
       </c>
@@ -25141,7 +25141,7 @@
       <c r="AD57" s="25"/>
       <c r="AE57" s="55"/>
       <c r="AG57" s="24"/>
-      <c r="AH57" s="269">
+      <c r="AH57" s="253">
         <f>Games!N52</f>
         <v>0.82</v>
       </c>
@@ -25149,7 +25149,7 @@
         <f>_xlfn.XLOOKUP(AJ57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ57" s="262" t="str">
+      <c r="AJ57" s="256" t="str">
         <f>Games!O34</f>
         <v>Connecticut</v>
       </c>
@@ -25171,7 +25171,7 @@
       <c r="AO57" s="17"/>
     </row>
     <row r="58" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="283">
+      <c r="A58" s="255">
         <f>IF($AU$5=TRUE,A54+1,"")</f>
         <v>14</v>
       </c>
@@ -25179,9 +25179,9 @@
       <c r="C58" s="38"/>
       <c r="D58" s="71"/>
       <c r="E58" s="49"/>
-      <c r="F58" s="263"/>
-      <c r="G58" s="248"/>
-      <c r="H58" s="278"/>
+      <c r="F58" s="257"/>
+      <c r="G58" s="260"/>
+      <c r="H58" s="262"/>
       <c r="I58" s="24"/>
       <c r="J58" s="24"/>
       <c r="K58" s="50"/>
@@ -25202,19 +25202,19 @@
       <c r="AD58" s="25"/>
       <c r="AE58" s="56"/>
       <c r="AG58" s="24"/>
-      <c r="AH58" s="270"/>
+      <c r="AH58" s="254"/>
       <c r="AI58" s="250"/>
-      <c r="AJ58" s="263"/>
+      <c r="AJ58" s="257"/>
       <c r="AK58" s="55"/>
       <c r="AM58" s="39"/>
       <c r="AN58" s="28"/>
-      <c r="AO58" s="287">
+      <c r="AO58" s="277">
         <f>IF($AU$5=TRUE,AO54+1,"")</f>
         <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="283"/>
+      <c r="A59" s="255"/>
       <c r="B59" s="27">
         <v>14</v>
       </c>
@@ -25232,21 +25232,21 @@
       </c>
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
-      <c r="I59" s="283">
+      <c r="I59" s="255">
         <f>IF($AU$5=TRUE,I43+1,"")</f>
         <v>52</v>
       </c>
       <c r="J59" s="15"/>
       <c r="K59" s="50"/>
-      <c r="L59" s="279" t="str">
+      <c r="L59" s="265" t="str">
         <f>Games!O58</f>
         <v>Duke</v>
       </c>
-      <c r="M59" s="247" t="e" vm="92">
+      <c r="M59" s="259" t="e" vm="92">
         <f>_xlfn.XLOOKUP(L59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N59" s="277">
+      <c r="N59" s="261">
         <f>Games!N65</f>
         <v>0.85</v>
       </c>
@@ -25260,7 +25260,7 @@
       <c r="W59" s="25"/>
       <c r="X59" s="25"/>
       <c r="AA59" s="25"/>
-      <c r="AB59" s="269">
+      <c r="AB59" s="253">
         <f>Games!N67</f>
         <v>0.97</v>
       </c>
@@ -25268,12 +25268,12 @@
         <f>_xlfn.XLOOKUP(AD59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD59" s="262" t="str">
+      <c r="AD59" s="256" t="str">
         <f>Games!O62</f>
         <v>Connecticut</v>
       </c>
       <c r="AE59" s="56"/>
-      <c r="AG59" s="283">
+      <c r="AG59" s="255">
         <f>IF($AU$5=TRUE,AG43+1,"")</f>
         <v>56</v>
       </c>
@@ -25293,7 +25293,7 @@
       <c r="AN59" s="27">
         <v>14</v>
       </c>
-      <c r="AO59" s="287"/>
+      <c r="AO59" s="277"/>
     </row>
     <row r="60" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="16"/>
@@ -25302,12 +25302,12 @@
       <c r="D60" s="71"/>
       <c r="F60" s="24"/>
       <c r="G60" s="24"/>
-      <c r="I60" s="283"/>
+      <c r="I60" s="255"/>
       <c r="J60" s="15"/>
       <c r="K60" s="50"/>
-      <c r="L60" s="280"/>
-      <c r="M60" s="248"/>
-      <c r="N60" s="278"/>
+      <c r="L60" s="266"/>
+      <c r="M60" s="260"/>
+      <c r="N60" s="262"/>
       <c r="O60" s="25"/>
       <c r="P60" s="25"/>
       <c r="Q60" s="25"/>
@@ -25319,11 +25319,11 @@
       <c r="W60" s="25"/>
       <c r="X60" s="25"/>
       <c r="AA60" s="25"/>
-      <c r="AB60" s="270"/>
+      <c r="AB60" s="254"/>
       <c r="AC60" s="250"/>
-      <c r="AD60" s="263"/>
+      <c r="AD60" s="257"/>
       <c r="AE60" s="56"/>
-      <c r="AG60" s="283"/>
+      <c r="AG60" s="255"/>
       <c r="AJ60" s="24"/>
       <c r="AM60" s="39"/>
       <c r="AN60" s="28"/>
@@ -25346,15 +25346,15 @@
         <f>Games!L19</f>
         <v>0.17</v>
       </c>
-      <c r="F61" s="262" t="str">
+      <c r="F61" s="256" t="str">
         <f>Games!O19</f>
         <v>Brigham Young</v>
       </c>
-      <c r="G61" s="247" t="e" vm="94">
+      <c r="G61" s="259" t="e" vm="94">
         <f>_xlfn.XLOOKUP(F61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H61" s="264">
+      <c r="H61" s="251">
         <f>Games!L45</f>
         <v>0.98</v>
       </c>
@@ -25377,7 +25377,7 @@
       <c r="AD61" s="25"/>
       <c r="AE61" s="56"/>
       <c r="AG61" s="24"/>
-      <c r="AH61" s="264">
+      <c r="AH61" s="251">
         <f>Games!L53</f>
         <v>0.36</v>
       </c>
@@ -25385,7 +25385,7 @@
         <f>_xlfn.XLOOKUP(AJ61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ61" s="262" t="str">
+      <c r="AJ61" s="256" t="str">
         <f>Games!O35</f>
         <v>Cornell</v>
       </c>
@@ -25407,7 +25407,7 @@
       <c r="AO61" s="17"/>
     </row>
     <row r="62" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="283">
+      <c r="A62" s="255">
         <f>IF($AU$5=TRUE,A58+1,"")</f>
         <v>15</v>
       </c>
@@ -25415,9 +25415,9 @@
       <c r="C62" s="38"/>
       <c r="D62" s="71"/>
       <c r="E62" s="49"/>
-      <c r="F62" s="263"/>
-      <c r="G62" s="248"/>
-      <c r="H62" s="265"/>
+      <c r="F62" s="257"/>
+      <c r="G62" s="260"/>
+      <c r="H62" s="252"/>
       <c r="I62" s="24"/>
       <c r="J62" s="24"/>
       <c r="K62" s="50"/>
@@ -25437,19 +25437,19 @@
       <c r="AD62" s="25"/>
       <c r="AE62" s="56"/>
       <c r="AG62" s="24"/>
-      <c r="AH62" s="265"/>
+      <c r="AH62" s="252"/>
       <c r="AI62" s="250"/>
-      <c r="AJ62" s="263"/>
+      <c r="AJ62" s="257"/>
       <c r="AK62" s="55"/>
       <c r="AM62" s="39"/>
       <c r="AN62" s="28"/>
-      <c r="AO62" s="287">
+      <c r="AO62" s="277">
         <f>IF($AU$5=TRUE,AO58+1,"")</f>
         <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="283"/>
+      <c r="A63" s="255"/>
       <c r="B63" s="27">
         <v>10</v>
       </c>
@@ -25465,21 +25465,21 @@
         <f>Games!N19</f>
         <v>0.83</v>
       </c>
-      <c r="F63" s="282">
+      <c r="F63" s="276">
         <f>IF($AU$5=TRUE,F55+1,"")</f>
         <v>40</v>
       </c>
       <c r="G63" s="14"/>
       <c r="H63" s="49"/>
-      <c r="I63" s="279" t="str">
+      <c r="I63" s="265" t="str">
         <f>Games!O45</f>
         <v>Brigham Young</v>
       </c>
-      <c r="J63" s="247" t="e" vm="94">
+      <c r="J63" s="259" t="e" vm="94">
         <f>_xlfn.XLOOKUP(I63,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K63" s="277">
+      <c r="K63" s="261">
         <f>Games!N58</f>
         <v>0.28999999999999998</v>
       </c>
@@ -25499,7 +25499,7 @@
       <c r="Z63" s="57"/>
       <c r="AA63" s="25"/>
       <c r="AD63" s="25"/>
-      <c r="AE63" s="269">
+      <c r="AE63" s="253">
         <f>Games!N62</f>
         <v>0.13</v>
       </c>
@@ -25507,13 +25507,13 @@
         <f>_xlfn.XLOOKUP(AG63,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG63" s="262" t="str">
+      <c r="AG63" s="256" t="str">
         <f>Games!O53</f>
         <v>Creighton</v>
       </c>
       <c r="AH63" s="55"/>
       <c r="AI63" s="51"/>
-      <c r="AJ63" s="282">
+      <c r="AJ63" s="276">
         <f>IF($AU$5=TRUE,AJ55+1,"")</f>
         <v>48</v>
       </c>
@@ -25532,19 +25532,19 @@
       <c r="AN63" s="27">
         <v>10</v>
       </c>
-      <c r="AO63" s="287"/>
+      <c r="AO63" s="277"/>
     </row>
     <row r="64" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="16"/>
       <c r="B64" s="28"/>
       <c r="C64" s="38"/>
       <c r="D64" s="71"/>
-      <c r="F64" s="283"/>
+      <c r="F64" s="255"/>
       <c r="G64" s="15"/>
       <c r="H64" s="50"/>
-      <c r="I64" s="280"/>
-      <c r="J64" s="248"/>
-      <c r="K64" s="278"/>
+      <c r="I64" s="266"/>
+      <c r="J64" s="260"/>
+      <c r="K64" s="262"/>
       <c r="L64" s="25"/>
       <c r="M64" s="25"/>
       <c r="O64" s="25"/>
@@ -25560,11 +25560,11 @@
       <c r="Z64" s="57"/>
       <c r="AA64" s="25"/>
       <c r="AD64" s="25"/>
-      <c r="AE64" s="270"/>
+      <c r="AE64" s="254"/>
       <c r="AF64" s="250"/>
-      <c r="AG64" s="263"/>
+      <c r="AG64" s="257"/>
       <c r="AH64" s="56"/>
-      <c r="AJ64" s="283"/>
+      <c r="AJ64" s="255"/>
       <c r="AM64" s="39"/>
       <c r="AN64" s="28"/>
       <c r="AO64" s="17"/>
@@ -25586,15 +25586,15 @@
         <f>Games!L20</f>
         <v>0.6</v>
       </c>
-      <c r="F65" s="262" t="str">
+      <c r="F65" s="256" t="str">
         <f>Games!O20</f>
         <v>Brown</v>
       </c>
-      <c r="G65" s="247" t="e" vm="95">
+      <c r="G65" s="259" t="e" vm="95">
         <f>_xlfn.XLOOKUP(F65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H65" s="277">
+      <c r="H65" s="261">
         <f>Games!N45</f>
         <v>0.02</v>
       </c>
@@ -25616,7 +25616,7 @@
       <c r="AA65" s="25"/>
       <c r="AD65" s="25"/>
       <c r="AG65" s="24"/>
-      <c r="AH65" s="269">
+      <c r="AH65" s="253">
         <f>Games!N53</f>
         <v>0.64</v>
       </c>
@@ -25624,7 +25624,7 @@
         <f>_xlfn.XLOOKUP(AJ65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ65" s="262" t="str">
+      <c r="AJ65" s="256" t="str">
         <f>Games!O36</f>
         <v>Creighton</v>
       </c>
@@ -25646,7 +25646,7 @@
       <c r="AO65" s="17"/>
     </row>
     <row r="66" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="283">
+      <c r="A66" s="255">
         <f>IF($AU$5=TRUE,A62+1,"")</f>
         <v>16</v>
       </c>
@@ -25654,41 +25654,41 @@
       <c r="C66" s="38"/>
       <c r="D66" s="71"/>
       <c r="E66" s="49"/>
-      <c r="F66" s="263"/>
-      <c r="G66" s="248"/>
-      <c r="H66" s="278"/>
+      <c r="F66" s="257"/>
+      <c r="G66" s="260"/>
+      <c r="H66" s="262"/>
       <c r="I66" s="25"/>
       <c r="J66" s="25"/>
       <c r="L66" s="25"/>
       <c r="M66" s="25"/>
-      <c r="O66" s="261"/>
-      <c r="P66" s="261"/>
-      <c r="Q66" s="261"/>
-      <c r="R66" s="261"/>
-      <c r="S66" s="261"/>
-      <c r="T66" s="261"/>
-      <c r="U66" s="261"/>
-      <c r="V66" s="261"/>
-      <c r="W66" s="261"/>
-      <c r="X66" s="261"/>
-      <c r="Y66" s="261"/>
-      <c r="Z66" s="261"/>
-      <c r="AA66" s="261"/>
+      <c r="O66" s="292"/>
+      <c r="P66" s="292"/>
+      <c r="Q66" s="292"/>
+      <c r="R66" s="292"/>
+      <c r="S66" s="292"/>
+      <c r="T66" s="292"/>
+      <c r="U66" s="292"/>
+      <c r="V66" s="292"/>
+      <c r="W66" s="292"/>
+      <c r="X66" s="292"/>
+      <c r="Y66" s="292"/>
+      <c r="Z66" s="292"/>
+      <c r="AA66" s="292"/>
       <c r="AD66" s="25"/>
       <c r="AG66" s="24"/>
-      <c r="AH66" s="270"/>
+      <c r="AH66" s="254"/>
       <c r="AI66" s="250"/>
-      <c r="AJ66" s="263"/>
+      <c r="AJ66" s="257"/>
       <c r="AK66" s="55"/>
       <c r="AM66" s="39"/>
       <c r="AN66" s="28"/>
-      <c r="AO66" s="287">
+      <c r="AO66" s="277">
         <f>IF($AU$5=TRUE,AO62+1,"")</f>
         <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="283"/>
+      <c r="A67" s="255"/>
       <c r="B67" s="27">
         <v>15</v>
       </c>
@@ -25710,19 +25710,19 @@
       <c r="J67" s="25"/>
       <c r="L67" s="25"/>
       <c r="M67" s="25"/>
-      <c r="O67" s="260"/>
-      <c r="P67" s="260"/>
-      <c r="Q67" s="260"/>
-      <c r="R67" s="260"/>
-      <c r="S67" s="260"/>
-      <c r="T67" s="260"/>
-      <c r="U67" s="260"/>
-      <c r="V67" s="260"/>
-      <c r="W67" s="260"/>
-      <c r="X67" s="260"/>
-      <c r="Y67" s="260"/>
-      <c r="Z67" s="260"/>
-      <c r="AA67" s="260"/>
+      <c r="O67" s="291"/>
+      <c r="P67" s="291"/>
+      <c r="Q67" s="291"/>
+      <c r="R67" s="291"/>
+      <c r="S67" s="291"/>
+      <c r="T67" s="291"/>
+      <c r="U67" s="291"/>
+      <c r="V67" s="291"/>
+      <c r="W67" s="291"/>
+      <c r="X67" s="291"/>
+      <c r="Y67" s="291"/>
+      <c r="Z67" s="291"/>
+      <c r="AA67" s="291"/>
       <c r="AD67" s="25"/>
       <c r="AG67" s="25"/>
       <c r="AJ67" s="24"/>
@@ -25741,7 +25741,7 @@
       <c r="AN67" s="27">
         <v>15</v>
       </c>
-      <c r="AO67" s="287"/>
+      <c r="AO67" s="277"/>
     </row>
     <row r="68" spans="1:41" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
@@ -25782,57 +25782,189 @@
     <row r="70" spans="1:41" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="258">
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="AI9:AI10"/>
-    <mergeCell ref="AI13:AI14"/>
-    <mergeCell ref="AI17:AI18"/>
-    <mergeCell ref="AI21:AI22"/>
-    <mergeCell ref="AI25:AI26"/>
-    <mergeCell ref="AI29:AI30"/>
-    <mergeCell ref="AI33:AI34"/>
-    <mergeCell ref="AI37:AI38"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AD19:AE20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="AG23:AG24"/>
-    <mergeCell ref="AE23:AE24"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AF23:AF24"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="AE31:AE32"/>
-    <mergeCell ref="N43:N44"/>
-    <mergeCell ref="T35:V35"/>
-    <mergeCell ref="AE55:AE56"/>
-    <mergeCell ref="AB43:AB44"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AD43:AD44"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="U39:U40"/>
-    <mergeCell ref="P51:P52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="V39:X40"/>
-    <mergeCell ref="AC43:AC44"/>
-    <mergeCell ref="AD27:AD28"/>
-    <mergeCell ref="AD59:AD60"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="AC27:AC28"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="R27:T28"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="Q51:Q52"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="T11:V19"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="O67:AA67"/>
+    <mergeCell ref="O66:AA66"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="K51:L52"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="AB27:AB28"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="S32:W33"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="S31:W31"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="AC59:AC60"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="B1:AN1"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AJ63:AJ64"/>
+    <mergeCell ref="AJ57:AJ58"/>
+    <mergeCell ref="AH65:AH66"/>
+    <mergeCell ref="AJ65:AJ66"/>
+    <mergeCell ref="AH61:AH62"/>
+    <mergeCell ref="AI41:AI42"/>
+    <mergeCell ref="AI45:AI46"/>
+    <mergeCell ref="AI49:AI50"/>
+    <mergeCell ref="AI53:AI54"/>
+    <mergeCell ref="AI57:AI58"/>
+    <mergeCell ref="AI61:AI62"/>
+    <mergeCell ref="AI65:AI66"/>
+    <mergeCell ref="AJ45:AJ46"/>
+    <mergeCell ref="AG39:AG40"/>
+    <mergeCell ref="AE63:AE64"/>
+    <mergeCell ref="AG63:AG64"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="AF63:AF64"/>
+    <mergeCell ref="AF55:AF56"/>
+    <mergeCell ref="AF47:AF48"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="AB59:AB60"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="AH29:AH30"/>
+    <mergeCell ref="AJ29:AJ30"/>
+    <mergeCell ref="AJ37:AJ38"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="AH45:AH46"/>
+    <mergeCell ref="AE47:AE48"/>
+    <mergeCell ref="AG59:AG60"/>
+    <mergeCell ref="AG55:AG56"/>
+    <mergeCell ref="AH57:AH58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="M59:M60"/>
+    <mergeCell ref="N59:N60"/>
+    <mergeCell ref="AO62:AO63"/>
+    <mergeCell ref="AO66:AO67"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="AO26:AO27"/>
+    <mergeCell ref="AO30:AO31"/>
+    <mergeCell ref="AO34:AO35"/>
+    <mergeCell ref="AJ61:AJ62"/>
+    <mergeCell ref="AE39:AE40"/>
+    <mergeCell ref="AH49:AH50"/>
+    <mergeCell ref="AJ49:AJ50"/>
+    <mergeCell ref="AH53:AH54"/>
+    <mergeCell ref="AJ53:AJ54"/>
+    <mergeCell ref="AJ47:AJ48"/>
+    <mergeCell ref="AD51:AE52"/>
+    <mergeCell ref="AG47:AG48"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="AO22:AO23"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="L59:L60"/>
+    <mergeCell ref="AO50:AO51"/>
+    <mergeCell ref="AO54:AO55"/>
+    <mergeCell ref="AO58:AO59"/>
+    <mergeCell ref="AO38:AO39"/>
+    <mergeCell ref="AO42:AO43"/>
+    <mergeCell ref="AO46:AO47"/>
+    <mergeCell ref="AJ41:AJ42"/>
+    <mergeCell ref="AJ39:AJ40"/>
+    <mergeCell ref="AH41:AH42"/>
+    <mergeCell ref="AH37:AH38"/>
+    <mergeCell ref="AJ55:AJ56"/>
     <mergeCell ref="AH25:AH26"/>
     <mergeCell ref="AH33:AH34"/>
     <mergeCell ref="AG43:AG44"/>
@@ -25857,189 +25989,57 @@
     <mergeCell ref="AG27:AG28"/>
     <mergeCell ref="AG31:AG32"/>
     <mergeCell ref="AJ33:AJ34"/>
-    <mergeCell ref="AO50:AO51"/>
-    <mergeCell ref="AO54:AO55"/>
-    <mergeCell ref="AO58:AO59"/>
-    <mergeCell ref="AO38:AO39"/>
-    <mergeCell ref="AO42:AO43"/>
-    <mergeCell ref="AO46:AO47"/>
-    <mergeCell ref="AJ41:AJ42"/>
-    <mergeCell ref="AJ39:AJ40"/>
-    <mergeCell ref="AH41:AH42"/>
-    <mergeCell ref="AH37:AH38"/>
-    <mergeCell ref="AJ55:AJ56"/>
-    <mergeCell ref="AO62:AO63"/>
-    <mergeCell ref="AO66:AO67"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="AO26:AO27"/>
-    <mergeCell ref="AO30:AO31"/>
-    <mergeCell ref="AO34:AO35"/>
-    <mergeCell ref="AJ61:AJ62"/>
-    <mergeCell ref="AE39:AE40"/>
-    <mergeCell ref="AH49:AH50"/>
-    <mergeCell ref="AJ49:AJ50"/>
-    <mergeCell ref="AH53:AH54"/>
-    <mergeCell ref="AJ53:AJ54"/>
-    <mergeCell ref="AJ47:AJ48"/>
-    <mergeCell ref="AD51:AE52"/>
-    <mergeCell ref="AG47:AG48"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="AO22:AO23"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="AH29:AH30"/>
-    <mergeCell ref="AJ29:AJ30"/>
-    <mergeCell ref="AJ37:AJ38"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="AH45:AH46"/>
-    <mergeCell ref="AE47:AE48"/>
-    <mergeCell ref="AG59:AG60"/>
-    <mergeCell ref="AG55:AG56"/>
-    <mergeCell ref="AH57:AH58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="M59:M60"/>
-    <mergeCell ref="N59:N60"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="AG39:AG40"/>
-    <mergeCell ref="AE63:AE64"/>
-    <mergeCell ref="AG63:AG64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="AF63:AF64"/>
-    <mergeCell ref="AF55:AF56"/>
-    <mergeCell ref="AF47:AF48"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="M43:M44"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="AB59:AB60"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="AJ63:AJ64"/>
-    <mergeCell ref="AJ57:AJ58"/>
-    <mergeCell ref="AH65:AH66"/>
-    <mergeCell ref="AJ65:AJ66"/>
-    <mergeCell ref="AH61:AH62"/>
-    <mergeCell ref="AI41:AI42"/>
-    <mergeCell ref="AI45:AI46"/>
-    <mergeCell ref="AI49:AI50"/>
-    <mergeCell ref="AI53:AI54"/>
-    <mergeCell ref="AI57:AI58"/>
-    <mergeCell ref="AI61:AI62"/>
-    <mergeCell ref="AI65:AI66"/>
-    <mergeCell ref="AJ45:AJ46"/>
-    <mergeCell ref="B1:AN1"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AJ9:AJ10"/>
-    <mergeCell ref="AH9:AH10"/>
-    <mergeCell ref="AJ13:AJ14"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="T11:V19"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="O67:AA67"/>
-    <mergeCell ref="O66:AA66"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="K51:L52"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="AB27:AB28"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="S32:W33"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="S31:W31"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="AC59:AC60"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="AD27:AD28"/>
+    <mergeCell ref="AD59:AD60"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="AC27:AC28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="R27:T28"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="Q51:Q52"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="AE31:AE32"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="AE55:AE56"/>
+    <mergeCell ref="AB43:AB44"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AD43:AD44"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="U39:U40"/>
+    <mergeCell ref="P51:P52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="V39:X40"/>
+    <mergeCell ref="AC43:AC44"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AD19:AE20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="AG23:AG24"/>
+    <mergeCell ref="AE23:AE24"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AF23:AF24"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="AI21:AI22"/>
+    <mergeCell ref="AI25:AI26"/>
+    <mergeCell ref="AI29:AI30"/>
+    <mergeCell ref="AI33:AI34"/>
+    <mergeCell ref="AI37:AI38"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
